--- a/12600717.xlsx
+++ b/12600717.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python CAP776 Excell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578502CE-C951-4027-96BE-047FE141D52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A72EA18-389E-4D17-94F4-42E6120596DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,18 @@
   </si>
   <si>
     <t>No classes; dedicated day to recovery, project coding, and leisure.</t>
+  </si>
+  <si>
+    <t>Relaxed</t>
+  </si>
+  <si>
+    <t>Highly Satisfied</t>
+  </si>
+  <si>
+    <t>Sunday break; reviewed weak concepts and prepared schedule for upcoming week.</t>
+  </si>
+  <si>
+    <t>Attended 5 classes; started week with solid momentum and evening coding session.</t>
   </si>
 </sst>
 </file>
@@ -1299,49 +1311,97 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+    <row r="12" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>46264</v>
+      </c>
+      <c r="B12" s="9">
+        <v>510</v>
+      </c>
+      <c r="C12" s="9">
+        <v>45</v>
+      </c>
+      <c r="D12" s="9">
+        <v>180</v>
+      </c>
+      <c r="E12" s="9">
+        <v>120</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>270</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1125</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+        <v>315</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B13" s="9">
+        <v>420</v>
+      </c>
+      <c r="C13" s="9">
+        <v>45</v>
+      </c>
+      <c r="D13" s="9">
+        <v>120</v>
+      </c>
+      <c r="E13" s="9">
+        <v>90</v>
+      </c>
+      <c r="F13" s="9">
+        <v>250</v>
+      </c>
+      <c r="G13" s="9">
+        <v>5</v>
+      </c>
+      <c r="H13" s="9">
+        <v>180</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1105</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>335</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/12600717.xlsx
+++ b/12600717.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python CAP776 Excell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A72EA18-389E-4D17-94F4-42E6120596DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D554F22D-AC97-466D-9447-D878E7722FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>Attended 5 classes; started week with solid momentum and evening coding session.</t>
+  </si>
+  <si>
+    <t>Attended 5 classes; stayed on track with coursework and made solid progress on programming tasks.</t>
   </si>
 </sst>
 </file>
@@ -1403,37 +1406,61 @@
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+    <row r="14" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B14" s="9">
+        <v>450</v>
+      </c>
+      <c r="C14" s="9">
+        <v>30</v>
+      </c>
+      <c r="D14" s="9">
+        <v>150</v>
+      </c>
+      <c r="E14" s="9">
+        <v>120</v>
+      </c>
+      <c r="F14" s="9">
+        <v>250</v>
+      </c>
+      <c r="G14" s="9">
+        <v>5</v>
+      </c>
+      <c r="H14" s="9">
+        <v>150</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
       <c r="I15" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1442,20 +1469,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
       <c r="I16" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1464,20 +1491,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="12"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
       <c r="I17" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1486,20 +1513,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="12"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
       <c r="I18" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1508,20 +1535,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
       <c r="I19" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1530,20 +1557,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="12"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
       <c r="I20" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1552,20 +1579,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
       <c r="I21" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1574,20 +1601,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
       <c r="I22" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1596,20 +1623,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="12"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
       <c r="I23" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1618,20 +1645,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="12"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
       <c r="I24" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1640,20 +1667,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="12"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
       <c r="I25" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1662,20 +1689,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="12"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
       <c r="I26" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1684,20 +1711,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="12"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
       <c r="I27" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1706,20 +1733,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="12"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
       <c r="I28" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1728,20 +1755,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="12"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
       <c r="I29" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1750,20 +1777,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
       <c r="I30" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1772,20 +1799,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="12"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
       <c r="I31" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1794,20 +1821,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="12"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
       <c r="I32" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1816,20 +1843,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="12"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
       <c r="I33" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1838,20 +1865,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="12"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
       <c r="I34" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1860,20 +1887,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="12"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
+      <c r="A35" s="8"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
       <c r="I35" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1882,20 +1909,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="12"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
+      <c r="A36" s="8"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
       <c r="I36" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1904,20 +1931,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="12"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
+      <c r="A37" s="8"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
       <c r="I37" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1926,20 +1953,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="12"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
+      <c r="A38" s="8"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
       <c r="I38" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1948,20 +1975,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="12"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
+      <c r="A39" s="8"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
       <c r="I39" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1970,20 +1997,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="12"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
+      <c r="A40" s="8"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
       <c r="I40" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1992,20 +2019,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="12"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
+      <c r="A41" s="8"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
       <c r="I41" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2014,20 +2041,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="12"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
+      <c r="A42" s="8"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
       <c r="I42" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2036,20 +2063,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="12"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
+      <c r="A43" s="8"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
       <c r="I43" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2058,20 +2085,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="12"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
+      <c r="A44" s="8"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
       <c r="I44" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2080,20 +2107,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="12"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
+      <c r="A45" s="8"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
       <c r="I45" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2102,20 +2129,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="12"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
+      <c r="A46" s="8"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
       <c r="I46" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2124,20 +2151,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="12"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
+      <c r="A47" s="8"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
       <c r="I47" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2146,20 +2173,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+      <c r="N47" s="12"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
+      <c r="A48" s="8"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
       <c r="I48" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2168,20 +2195,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="12"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
+      <c r="A49" s="8"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
       <c r="I49" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2190,20 +2217,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="12"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
+      <c r="A50" s="8"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9"/>
       <c r="I50" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2212,20 +2239,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="12"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
+      <c r="A51" s="8"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9"/>
       <c r="I51" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2234,20 +2261,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+      <c r="N51" s="12"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
+      <c r="A52" s="8"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
       <c r="I52" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2256,20 +2283,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+      <c r="N52" s="12"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
+      <c r="A53" s="8"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9"/>
       <c r="I53" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2278,20 +2305,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="12"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
+      <c r="A54" s="8"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
       <c r="I54" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2300,20 +2327,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="11"/>
+      <c r="N54" s="12"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
+      <c r="A55" s="8"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
       <c r="I55" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2322,20 +2349,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="12"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
+      <c r="A56" s="8"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
       <c r="I56" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2344,20 +2371,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+      <c r="N56" s="12"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
+      <c r="A57" s="8"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
       <c r="I57" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2366,20 +2393,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
+      <c r="N57" s="12"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
+      <c r="A58" s="8"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
       <c r="I58" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2388,20 +2415,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+      <c r="K58" s="11"/>
+      <c r="L58" s="11"/>
+      <c r="M58" s="11"/>
+      <c r="N58" s="12"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
+      <c r="A59" s="8"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
       <c r="I59" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2410,20 +2437,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="11"/>
+      <c r="N59" s="12"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
+      <c r="A60" s="8"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
       <c r="I60" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2432,20 +2459,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
+      <c r="N60" s="12"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
+      <c r="A61" s="8"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9"/>
       <c r="I61" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2454,20 +2481,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+      <c r="K61" s="11"/>
+      <c r="L61" s="11"/>
+      <c r="M61" s="11"/>
+      <c r="N61" s="12"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
+      <c r="A62" s="8"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="9"/>
       <c r="I62" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2476,20 +2503,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="11"/>
+      <c r="M62" s="11"/>
+      <c r="N62" s="12"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
+      <c r="A63" s="8"/>
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9"/>
+      <c r="F63" s="9"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="9"/>
       <c r="I63" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2498,20 +2525,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+      <c r="K63" s="11"/>
+      <c r="L63" s="11"/>
+      <c r="M63" s="11"/>
+      <c r="N63" s="12"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
+      <c r="A64" s="8"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
       <c r="I64" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2520,20 +2547,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+      <c r="K64" s="11"/>
+      <c r="L64" s="11"/>
+      <c r="M64" s="11"/>
+      <c r="N64" s="12"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
+      <c r="A65" s="8"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
       <c r="I65" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2542,20 +2569,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11"/>
+      <c r="N65" s="12"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
+      <c r="A66" s="8"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="9"/>
       <c r="I66" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2564,20 +2591,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="11"/>
+      <c r="N66" s="12"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
+      <c r="A67" s="8"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="9"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="9"/>
+      <c r="H67" s="9"/>
       <c r="I67" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2586,20 +2613,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="11"/>
+      <c r="N67" s="12"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
+      <c r="A68" s="8"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="9"/>
       <c r="I68" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2608,20 +2635,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
+      <c r="K68" s="11"/>
+      <c r="L68" s="11"/>
+      <c r="M68" s="11"/>
+      <c r="N68" s="12"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
+      <c r="A69" s="8"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="9"/>
+      <c r="H69" s="9"/>
       <c r="I69" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2630,20 +2657,20 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="17"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="11"/>
+      <c r="M69" s="11"/>
+      <c r="N69" s="12"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
+      <c r="A70" s="8"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="9"/>
+      <c r="H70" s="9"/>
       <c r="I70" s="15" t="str">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
@@ -2652,20 +2679,20 @@
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="17"/>
+      <c r="K70" s="11"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="12"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
+      <c r="A71" s="8"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="9"/>
       <c r="I71" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2674,20 +2701,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="17"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="11"/>
+      <c r="M71" s="11"/>
+      <c r="N71" s="12"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
+      <c r="A72" s="8"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="9"/>
+      <c r="H72" s="9"/>
       <c r="I72" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2696,20 +2723,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="17"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="11"/>
+      <c r="M72" s="11"/>
+      <c r="N72" s="12"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
+      <c r="A73" s="8"/>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="9"/>
+      <c r="F73" s="9"/>
+      <c r="G73" s="9"/>
+      <c r="H73" s="9"/>
       <c r="I73" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2718,20 +2745,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="17"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="11"/>
+      <c r="M73" s="11"/>
+      <c r="N73" s="12"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
+      <c r="A74" s="8"/>
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="9"/>
+      <c r="F74" s="9"/>
+      <c r="G74" s="9"/>
+      <c r="H74" s="9"/>
       <c r="I74" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2740,20 +2767,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="17"/>
+      <c r="K74" s="11"/>
+      <c r="L74" s="11"/>
+      <c r="M74" s="11"/>
+      <c r="N74" s="12"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
+      <c r="A75" s="8"/>
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="9"/>
+      <c r="E75" s="9"/>
+      <c r="F75" s="9"/>
+      <c r="G75" s="9"/>
+      <c r="H75" s="9"/>
       <c r="I75" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2762,20 +2789,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
-      <c r="N75" s="17"/>
+      <c r="K75" s="11"/>
+      <c r="L75" s="11"/>
+      <c r="M75" s="11"/>
+      <c r="N75" s="12"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
+      <c r="A76" s="8"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="9"/>
+      <c r="E76" s="9"/>
+      <c r="F76" s="9"/>
+      <c r="G76" s="9"/>
+      <c r="H76" s="9"/>
       <c r="I76" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2784,20 +2811,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
-      <c r="N76" s="17"/>
+      <c r="K76" s="11"/>
+      <c r="L76" s="11"/>
+      <c r="M76" s="11"/>
+      <c r="N76" s="12"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
+      <c r="A77" s="8"/>
+      <c r="B77" s="9"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
       <c r="I77" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2806,20 +2833,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
-      <c r="N77" s="17"/>
+      <c r="K77" s="11"/>
+      <c r="L77" s="11"/>
+      <c r="M77" s="11"/>
+      <c r="N77" s="12"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="13"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
+      <c r="A78" s="8"/>
+      <c r="B78" s="9"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="9"/>
       <c r="I78" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2828,20 +2855,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
-      <c r="N78" s="17"/>
+      <c r="K78" s="11"/>
+      <c r="L78" s="11"/>
+      <c r="M78" s="11"/>
+      <c r="N78" s="12"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="13"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
+      <c r="A79" s="8"/>
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
+      <c r="G79" s="9"/>
+      <c r="H79" s="9"/>
       <c r="I79" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2850,20 +2877,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
-      <c r="N79" s="17"/>
+      <c r="K79" s="11"/>
+      <c r="L79" s="11"/>
+      <c r="M79" s="11"/>
+      <c r="N79" s="12"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="13"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
+      <c r="A80" s="8"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
+      <c r="G80" s="9"/>
+      <c r="H80" s="9"/>
       <c r="I80" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2872,20 +2899,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K80" s="16"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="16"/>
-      <c r="N80" s="17"/>
+      <c r="K80" s="11"/>
+      <c r="L80" s="11"/>
+      <c r="M80" s="11"/>
+      <c r="N80" s="12"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="13"/>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
+      <c r="A81" s="8"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9"/>
+      <c r="G81" s="9"/>
+      <c r="H81" s="9"/>
       <c r="I81" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2894,20 +2921,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K81" s="16"/>
-      <c r="L81" s="16"/>
-      <c r="M81" s="16"/>
-      <c r="N81" s="17"/>
+      <c r="K81" s="11"/>
+      <c r="L81" s="11"/>
+      <c r="M81" s="11"/>
+      <c r="N81" s="12"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A82" s="13"/>
-      <c r="B82" s="14"/>
-      <c r="C82" s="14"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
+      <c r="A82" s="8"/>
+      <c r="B82" s="9"/>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="9"/>
+      <c r="F82" s="9"/>
+      <c r="G82" s="9"/>
+      <c r="H82" s="9"/>
       <c r="I82" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2916,20 +2943,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K82" s="16"/>
-      <c r="L82" s="16"/>
-      <c r="M82" s="16"/>
-      <c r="N82" s="17"/>
+      <c r="K82" s="11"/>
+      <c r="L82" s="11"/>
+      <c r="M82" s="11"/>
+      <c r="N82" s="12"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A83" s="13"/>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
+      <c r="A83" s="8"/>
+      <c r="B83" s="9"/>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="9"/>
+      <c r="F83" s="9"/>
+      <c r="G83" s="9"/>
+      <c r="H83" s="9"/>
       <c r="I83" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2938,20 +2965,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K83" s="16"/>
-      <c r="L83" s="16"/>
-      <c r="M83" s="16"/>
-      <c r="N83" s="17"/>
+      <c r="K83" s="11"/>
+      <c r="L83" s="11"/>
+      <c r="M83" s="11"/>
+      <c r="N83" s="12"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A84" s="13"/>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
+      <c r="A84" s="8"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9"/>
+      <c r="E84" s="9"/>
+      <c r="F84" s="9"/>
+      <c r="G84" s="9"/>
+      <c r="H84" s="9"/>
       <c r="I84" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2960,20 +2987,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K84" s="16"/>
-      <c r="L84" s="16"/>
-      <c r="M84" s="16"/>
-      <c r="N84" s="17"/>
+      <c r="K84" s="11"/>
+      <c r="L84" s="11"/>
+      <c r="M84" s="11"/>
+      <c r="N84" s="12"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A85" s="13"/>
-      <c r="B85" s="14"/>
-      <c r="C85" s="14"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
-      <c r="H85" s="14"/>
+      <c r="A85" s="8"/>
+      <c r="B85" s="9"/>
+      <c r="C85" s="9"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9"/>
+      <c r="G85" s="9"/>
+      <c r="H85" s="9"/>
       <c r="I85" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2982,20 +3009,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K85" s="16"/>
-      <c r="L85" s="16"/>
-      <c r="M85" s="16"/>
-      <c r="N85" s="17"/>
+      <c r="K85" s="11"/>
+      <c r="L85" s="11"/>
+      <c r="M85" s="11"/>
+      <c r="N85" s="12"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A86" s="13"/>
-      <c r="B86" s="14"/>
-      <c r="C86" s="14"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
-      <c r="H86" s="14"/>
+      <c r="A86" s="8"/>
+      <c r="B86" s="9"/>
+      <c r="C86" s="9"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="9"/>
+      <c r="F86" s="9"/>
+      <c r="G86" s="9"/>
+      <c r="H86" s="9"/>
       <c r="I86" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3004,20 +3031,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K86" s="16"/>
-      <c r="L86" s="16"/>
-      <c r="M86" s="16"/>
-      <c r="N86" s="17"/>
+      <c r="K86" s="11"/>
+      <c r="L86" s="11"/>
+      <c r="M86" s="11"/>
+      <c r="N86" s="12"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A87" s="13"/>
-      <c r="B87" s="14"/>
-      <c r="C87" s="14"/>
-      <c r="D87" s="14"/>
-      <c r="E87" s="14"/>
-      <c r="F87" s="14"/>
-      <c r="G87" s="14"/>
-      <c r="H87" s="14"/>
+      <c r="A87" s="8"/>
+      <c r="B87" s="9"/>
+      <c r="C87" s="9"/>
+      <c r="D87" s="9"/>
+      <c r="E87" s="9"/>
+      <c r="F87" s="9"/>
+      <c r="G87" s="9"/>
+      <c r="H87" s="9"/>
       <c r="I87" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3026,20 +3053,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K87" s="16"/>
-      <c r="L87" s="16"/>
-      <c r="M87" s="16"/>
-      <c r="N87" s="17"/>
+      <c r="K87" s="11"/>
+      <c r="L87" s="11"/>
+      <c r="M87" s="11"/>
+      <c r="N87" s="12"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A88" s="13"/>
-      <c r="B88" s="14"/>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="H88" s="14"/>
+      <c r="A88" s="8"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="9"/>
+      <c r="D88" s="9"/>
+      <c r="E88" s="9"/>
+      <c r="F88" s="9"/>
+      <c r="G88" s="9"/>
+      <c r="H88" s="9"/>
       <c r="I88" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3048,20 +3075,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K88" s="16"/>
-      <c r="L88" s="16"/>
-      <c r="M88" s="16"/>
-      <c r="N88" s="17"/>
+      <c r="K88" s="11"/>
+      <c r="L88" s="11"/>
+      <c r="M88" s="11"/>
+      <c r="N88" s="12"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A89" s="13"/>
-      <c r="B89" s="14"/>
-      <c r="C89" s="14"/>
-      <c r="D89" s="14"/>
-      <c r="E89" s="14"/>
-      <c r="F89" s="14"/>
-      <c r="G89" s="14"/>
-      <c r="H89" s="14"/>
+      <c r="A89" s="8"/>
+      <c r="B89" s="9"/>
+      <c r="C89" s="9"/>
+      <c r="D89" s="9"/>
+      <c r="E89" s="9"/>
+      <c r="F89" s="9"/>
+      <c r="G89" s="9"/>
+      <c r="H89" s="9"/>
       <c r="I89" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3070,20 +3097,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K89" s="16"/>
-      <c r="L89" s="16"/>
-      <c r="M89" s="16"/>
-      <c r="N89" s="17"/>
+      <c r="K89" s="11"/>
+      <c r="L89" s="11"/>
+      <c r="M89" s="11"/>
+      <c r="N89" s="12"/>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A90" s="13"/>
-      <c r="B90" s="14"/>
-      <c r="C90" s="14"/>
-      <c r="D90" s="14"/>
-      <c r="E90" s="14"/>
-      <c r="F90" s="14"/>
-      <c r="G90" s="14"/>
-      <c r="H90" s="14"/>
+      <c r="A90" s="8"/>
+      <c r="B90" s="9"/>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="9"/>
+      <c r="F90" s="9"/>
+      <c r="G90" s="9"/>
+      <c r="H90" s="9"/>
       <c r="I90" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3092,20 +3119,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K90" s="16"/>
-      <c r="L90" s="16"/>
-      <c r="M90" s="16"/>
-      <c r="N90" s="17"/>
+      <c r="K90" s="11"/>
+      <c r="L90" s="11"/>
+      <c r="M90" s="11"/>
+      <c r="N90" s="12"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A91" s="13"/>
-      <c r="B91" s="14"/>
-      <c r="C91" s="14"/>
-      <c r="D91" s="14"/>
-      <c r="E91" s="14"/>
-      <c r="F91" s="14"/>
-      <c r="G91" s="14"/>
-      <c r="H91" s="14"/>
+      <c r="A91" s="8"/>
+      <c r="B91" s="9"/>
+      <c r="C91" s="9"/>
+      <c r="D91" s="9"/>
+      <c r="E91" s="9"/>
+      <c r="F91" s="9"/>
+      <c r="G91" s="9"/>
+      <c r="H91" s="9"/>
       <c r="I91" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3114,20 +3141,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K91" s="16"/>
-      <c r="L91" s="16"/>
-      <c r="M91" s="16"/>
-      <c r="N91" s="17"/>
+      <c r="K91" s="11"/>
+      <c r="L91" s="11"/>
+      <c r="M91" s="11"/>
+      <c r="N91" s="12"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A92" s="13"/>
-      <c r="B92" s="14"/>
-      <c r="C92" s="14"/>
-      <c r="D92" s="14"/>
-      <c r="E92" s="14"/>
-      <c r="F92" s="14"/>
-      <c r="G92" s="14"/>
-      <c r="H92" s="14"/>
+      <c r="A92" s="8"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="9"/>
+      <c r="D92" s="9"/>
+      <c r="E92" s="9"/>
+      <c r="F92" s="9"/>
+      <c r="G92" s="9"/>
+      <c r="H92" s="9"/>
       <c r="I92" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3136,20 +3163,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K92" s="16"/>
-      <c r="L92" s="16"/>
-      <c r="M92" s="16"/>
-      <c r="N92" s="17"/>
+      <c r="K92" s="11"/>
+      <c r="L92" s="11"/>
+      <c r="M92" s="11"/>
+      <c r="N92" s="12"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A93" s="13"/>
-      <c r="B93" s="14"/>
-      <c r="C93" s="14"/>
-      <c r="D93" s="14"/>
-      <c r="E93" s="14"/>
-      <c r="F93" s="14"/>
-      <c r="G93" s="14"/>
-      <c r="H93" s="14"/>
+      <c r="A93" s="8"/>
+      <c r="B93" s="9"/>
+      <c r="C93" s="9"/>
+      <c r="D93" s="9"/>
+      <c r="E93" s="9"/>
+      <c r="F93" s="9"/>
+      <c r="G93" s="9"/>
+      <c r="H93" s="9"/>
       <c r="I93" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3158,20 +3185,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K93" s="16"/>
-      <c r="L93" s="16"/>
-      <c r="M93" s="16"/>
-      <c r="N93" s="17"/>
+      <c r="K93" s="11"/>
+      <c r="L93" s="11"/>
+      <c r="M93" s="11"/>
+      <c r="N93" s="12"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A94" s="13"/>
-      <c r="B94" s="14"/>
-      <c r="C94" s="14"/>
-      <c r="D94" s="14"/>
-      <c r="E94" s="14"/>
-      <c r="F94" s="14"/>
-      <c r="G94" s="14"/>
-      <c r="H94" s="14"/>
+      <c r="A94" s="8"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="9"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="9"/>
+      <c r="F94" s="9"/>
+      <c r="G94" s="9"/>
+      <c r="H94" s="9"/>
       <c r="I94" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3180,20 +3207,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K94" s="16"/>
-      <c r="L94" s="16"/>
-      <c r="M94" s="16"/>
-      <c r="N94" s="17"/>
+      <c r="K94" s="11"/>
+      <c r="L94" s="11"/>
+      <c r="M94" s="11"/>
+      <c r="N94" s="12"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A95" s="13"/>
-      <c r="B95" s="14"/>
-      <c r="C95" s="14"/>
-      <c r="D95" s="14"/>
-      <c r="E95" s="14"/>
-      <c r="F95" s="14"/>
-      <c r="G95" s="14"/>
-      <c r="H95" s="14"/>
+      <c r="A95" s="8"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="9"/>
+      <c r="H95" s="9"/>
       <c r="I95" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3202,20 +3229,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K95" s="16"/>
-      <c r="L95" s="16"/>
-      <c r="M95" s="16"/>
-      <c r="N95" s="17"/>
+      <c r="K95" s="11"/>
+      <c r="L95" s="11"/>
+      <c r="M95" s="11"/>
+      <c r="N95" s="12"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A96" s="13"/>
-      <c r="B96" s="14"/>
-      <c r="C96" s="14"/>
-      <c r="D96" s="14"/>
-      <c r="E96" s="14"/>
-      <c r="F96" s="14"/>
-      <c r="G96" s="14"/>
-      <c r="H96" s="14"/>
+      <c r="A96" s="8"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="9"/>
+      <c r="D96" s="9"/>
+      <c r="E96" s="9"/>
+      <c r="F96" s="9"/>
+      <c r="G96" s="9"/>
+      <c r="H96" s="9"/>
       <c r="I96" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3224,20 +3251,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K96" s="16"/>
-      <c r="L96" s="16"/>
-      <c r="M96" s="16"/>
-      <c r="N96" s="17"/>
+      <c r="K96" s="11"/>
+      <c r="L96" s="11"/>
+      <c r="M96" s="11"/>
+      <c r="N96" s="12"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A97" s="13"/>
-      <c r="B97" s="14"/>
-      <c r="C97" s="14"/>
-      <c r="D97" s="14"/>
-      <c r="E97" s="14"/>
-      <c r="F97" s="14"/>
-      <c r="G97" s="14"/>
-      <c r="H97" s="14"/>
+      <c r="A97" s="8"/>
+      <c r="B97" s="9"/>
+      <c r="C97" s="9"/>
+      <c r="D97" s="9"/>
+      <c r="E97" s="9"/>
+      <c r="F97" s="9"/>
+      <c r="G97" s="9"/>
+      <c r="H97" s="9"/>
       <c r="I97" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3246,20 +3273,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K97" s="16"/>
-      <c r="L97" s="16"/>
-      <c r="M97" s="16"/>
-      <c r="N97" s="17"/>
+      <c r="K97" s="11"/>
+      <c r="L97" s="11"/>
+      <c r="M97" s="11"/>
+      <c r="N97" s="12"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A98" s="13"/>
-      <c r="B98" s="14"/>
-      <c r="C98" s="14"/>
-      <c r="D98" s="14"/>
-      <c r="E98" s="14"/>
-      <c r="F98" s="14"/>
-      <c r="G98" s="14"/>
-      <c r="H98" s="14"/>
+      <c r="A98" s="8"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="9"/>
+      <c r="F98" s="9"/>
+      <c r="G98" s="9"/>
+      <c r="H98" s="9"/>
       <c r="I98" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3268,20 +3295,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K98" s="16"/>
-      <c r="L98" s="16"/>
-      <c r="M98" s="16"/>
-      <c r="N98" s="17"/>
+      <c r="K98" s="11"/>
+      <c r="L98" s="11"/>
+      <c r="M98" s="11"/>
+      <c r="N98" s="12"/>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A99" s="13"/>
-      <c r="B99" s="14"/>
-      <c r="C99" s="14"/>
-      <c r="D99" s="14"/>
-      <c r="E99" s="14"/>
-      <c r="F99" s="14"/>
-      <c r="G99" s="14"/>
-      <c r="H99" s="14"/>
+      <c r="A99" s="8"/>
+      <c r="B99" s="9"/>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="9"/>
+      <c r="F99" s="9"/>
+      <c r="G99" s="9"/>
+      <c r="H99" s="9"/>
       <c r="I99" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3290,20 +3317,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K99" s="16"/>
-      <c r="L99" s="16"/>
-      <c r="M99" s="16"/>
-      <c r="N99" s="17"/>
+      <c r="K99" s="11"/>
+      <c r="L99" s="11"/>
+      <c r="M99" s="11"/>
+      <c r="N99" s="12"/>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A100" s="13"/>
-      <c r="B100" s="14"/>
-      <c r="C100" s="14"/>
-      <c r="D100" s="14"/>
-      <c r="E100" s="14"/>
-      <c r="F100" s="14"/>
-      <c r="G100" s="14"/>
-      <c r="H100" s="14"/>
+      <c r="A100" s="8"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="9"/>
+      <c r="D100" s="9"/>
+      <c r="E100" s="9"/>
+      <c r="F100" s="9"/>
+      <c r="G100" s="9"/>
+      <c r="H100" s="9"/>
       <c r="I100" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3312,20 +3339,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K100" s="16"/>
-      <c r="L100" s="16"/>
-      <c r="M100" s="16"/>
-      <c r="N100" s="17"/>
+      <c r="K100" s="11"/>
+      <c r="L100" s="11"/>
+      <c r="M100" s="11"/>
+      <c r="N100" s="12"/>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A101" s="13"/>
-      <c r="B101" s="14"/>
-      <c r="C101" s="14"/>
-      <c r="D101" s="14"/>
-      <c r="E101" s="14"/>
-      <c r="F101" s="14"/>
-      <c r="G101" s="14"/>
-      <c r="H101" s="14"/>
+      <c r="A101" s="8"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9"/>
+      <c r="E101" s="9"/>
+      <c r="F101" s="9"/>
+      <c r="G101" s="9"/>
+      <c r="H101" s="9"/>
       <c r="I101" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3334,20 +3361,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K101" s="16"/>
-      <c r="L101" s="16"/>
-      <c r="M101" s="16"/>
-      <c r="N101" s="17"/>
+      <c r="K101" s="11"/>
+      <c r="L101" s="11"/>
+      <c r="M101" s="11"/>
+      <c r="N101" s="12"/>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A102" s="13"/>
-      <c r="B102" s="14"/>
-      <c r="C102" s="14"/>
-      <c r="D102" s="14"/>
-      <c r="E102" s="14"/>
-      <c r="F102" s="14"/>
-      <c r="G102" s="14"/>
-      <c r="H102" s="14"/>
+      <c r="A102" s="8"/>
+      <c r="B102" s="9"/>
+      <c r="C102" s="9"/>
+      <c r="D102" s="9"/>
+      <c r="E102" s="9"/>
+      <c r="F102" s="9"/>
+      <c r="G102" s="9"/>
+      <c r="H102" s="9"/>
       <c r="I102" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3356,20 +3383,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K102" s="16"/>
-      <c r="L102" s="16"/>
-      <c r="M102" s="16"/>
-      <c r="N102" s="17"/>
+      <c r="K102" s="11"/>
+      <c r="L102" s="11"/>
+      <c r="M102" s="11"/>
+      <c r="N102" s="12"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A103" s="13"/>
-      <c r="B103" s="14"/>
-      <c r="C103" s="14"/>
-      <c r="D103" s="14"/>
-      <c r="E103" s="14"/>
-      <c r="F103" s="14"/>
-      <c r="G103" s="14"/>
-      <c r="H103" s="14"/>
+      <c r="A103" s="8"/>
+      <c r="B103" s="9"/>
+      <c r="C103" s="9"/>
+      <c r="D103" s="9"/>
+      <c r="E103" s="9"/>
+      <c r="F103" s="9"/>
+      <c r="G103" s="9"/>
+      <c r="H103" s="9"/>
       <c r="I103" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3378,20 +3405,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K103" s="16"/>
-      <c r="L103" s="16"/>
-      <c r="M103" s="16"/>
-      <c r="N103" s="17"/>
+      <c r="K103" s="11"/>
+      <c r="L103" s="11"/>
+      <c r="M103" s="11"/>
+      <c r="N103" s="12"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A104" s="13"/>
-      <c r="B104" s="14"/>
-      <c r="C104" s="14"/>
-      <c r="D104" s="14"/>
-      <c r="E104" s="14"/>
-      <c r="F104" s="14"/>
-      <c r="G104" s="14"/>
-      <c r="H104" s="14"/>
+      <c r="A104" s="8"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="9"/>
+      <c r="D104" s="9"/>
+      <c r="E104" s="9"/>
+      <c r="F104" s="9"/>
+      <c r="G104" s="9"/>
+      <c r="H104" s="9"/>
       <c r="I104" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3400,20 +3427,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K104" s="16"/>
-      <c r="L104" s="16"/>
-      <c r="M104" s="16"/>
-      <c r="N104" s="17"/>
+      <c r="K104" s="11"/>
+      <c r="L104" s="11"/>
+      <c r="M104" s="11"/>
+      <c r="N104" s="12"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A105" s="13"/>
-      <c r="B105" s="14"/>
-      <c r="C105" s="14"/>
-      <c r="D105" s="14"/>
-      <c r="E105" s="14"/>
-      <c r="F105" s="14"/>
-      <c r="G105" s="14"/>
-      <c r="H105" s="14"/>
+      <c r="A105" s="8"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="9"/>
+      <c r="D105" s="9"/>
+      <c r="E105" s="9"/>
+      <c r="F105" s="9"/>
+      <c r="G105" s="9"/>
+      <c r="H105" s="9"/>
       <c r="I105" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3422,20 +3449,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K105" s="16"/>
-      <c r="L105" s="16"/>
-      <c r="M105" s="16"/>
-      <c r="N105" s="17"/>
+      <c r="K105" s="11"/>
+      <c r="L105" s="11"/>
+      <c r="M105" s="11"/>
+      <c r="N105" s="12"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A106" s="13"/>
-      <c r="B106" s="14"/>
-      <c r="C106" s="14"/>
-      <c r="D106" s="14"/>
-      <c r="E106" s="14"/>
-      <c r="F106" s="14"/>
-      <c r="G106" s="14"/>
-      <c r="H106" s="14"/>
+      <c r="A106" s="8"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="9"/>
+      <c r="D106" s="9"/>
+      <c r="E106" s="9"/>
+      <c r="F106" s="9"/>
+      <c r="G106" s="9"/>
+      <c r="H106" s="9"/>
       <c r="I106" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3444,20 +3471,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K106" s="16"/>
-      <c r="L106" s="16"/>
-      <c r="M106" s="16"/>
-      <c r="N106" s="17"/>
+      <c r="K106" s="11"/>
+      <c r="L106" s="11"/>
+      <c r="M106" s="11"/>
+      <c r="N106" s="12"/>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A107" s="13"/>
-      <c r="B107" s="14"/>
-      <c r="C107" s="14"/>
-      <c r="D107" s="14"/>
-      <c r="E107" s="14"/>
-      <c r="F107" s="14"/>
-      <c r="G107" s="14"/>
-      <c r="H107" s="14"/>
+      <c r="A107" s="8"/>
+      <c r="B107" s="9"/>
+      <c r="C107" s="9"/>
+      <c r="D107" s="9"/>
+      <c r="E107" s="9"/>
+      <c r="F107" s="9"/>
+      <c r="G107" s="9"/>
+      <c r="H107" s="9"/>
       <c r="I107" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3466,20 +3493,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K107" s="16"/>
-      <c r="L107" s="16"/>
-      <c r="M107" s="16"/>
-      <c r="N107" s="17"/>
+      <c r="K107" s="11"/>
+      <c r="L107" s="11"/>
+      <c r="M107" s="11"/>
+      <c r="N107" s="12"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A108" s="13"/>
-      <c r="B108" s="14"/>
-      <c r="C108" s="14"/>
-      <c r="D108" s="14"/>
-      <c r="E108" s="14"/>
-      <c r="F108" s="14"/>
-      <c r="G108" s="14"/>
-      <c r="H108" s="14"/>
+      <c r="A108" s="8"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="9"/>
+      <c r="D108" s="9"/>
+      <c r="E108" s="9"/>
+      <c r="F108" s="9"/>
+      <c r="G108" s="9"/>
+      <c r="H108" s="9"/>
       <c r="I108" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3488,20 +3515,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K108" s="16"/>
-      <c r="L108" s="16"/>
-      <c r="M108" s="16"/>
-      <c r="N108" s="17"/>
+      <c r="K108" s="11"/>
+      <c r="L108" s="11"/>
+      <c r="M108" s="11"/>
+      <c r="N108" s="12"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A109" s="13"/>
-      <c r="B109" s="14"/>
-      <c r="C109" s="14"/>
-      <c r="D109" s="14"/>
-      <c r="E109" s="14"/>
-      <c r="F109" s="14"/>
-      <c r="G109" s="14"/>
-      <c r="H109" s="14"/>
+      <c r="A109" s="8"/>
+      <c r="B109" s="9"/>
+      <c r="C109" s="9"/>
+      <c r="D109" s="9"/>
+      <c r="E109" s="9"/>
+      <c r="F109" s="9"/>
+      <c r="G109" s="9"/>
+      <c r="H109" s="9"/>
       <c r="I109" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3510,20 +3537,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K109" s="16"/>
-      <c r="L109" s="16"/>
-      <c r="M109" s="16"/>
-      <c r="N109" s="17"/>
+      <c r="K109" s="11"/>
+      <c r="L109" s="11"/>
+      <c r="M109" s="11"/>
+      <c r="N109" s="12"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A110" s="13"/>
-      <c r="B110" s="14"/>
-      <c r="C110" s="14"/>
-      <c r="D110" s="14"/>
-      <c r="E110" s="14"/>
-      <c r="F110" s="14"/>
-      <c r="G110" s="14"/>
-      <c r="H110" s="14"/>
+      <c r="A110" s="8"/>
+      <c r="B110" s="9"/>
+      <c r="C110" s="9"/>
+      <c r="D110" s="9"/>
+      <c r="E110" s="9"/>
+      <c r="F110" s="9"/>
+      <c r="G110" s="9"/>
+      <c r="H110" s="9"/>
       <c r="I110" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3532,20 +3559,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K110" s="16"/>
-      <c r="L110" s="16"/>
-      <c r="M110" s="16"/>
-      <c r="N110" s="17"/>
+      <c r="K110" s="11"/>
+      <c r="L110" s="11"/>
+      <c r="M110" s="11"/>
+      <c r="N110" s="12"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A111" s="13"/>
-      <c r="B111" s="14"/>
-      <c r="C111" s="14"/>
-      <c r="D111" s="14"/>
-      <c r="E111" s="14"/>
-      <c r="F111" s="14"/>
-      <c r="G111" s="14"/>
-      <c r="H111" s="14"/>
+      <c r="A111" s="8"/>
+      <c r="B111" s="9"/>
+      <c r="C111" s="9"/>
+      <c r="D111" s="9"/>
+      <c r="E111" s="9"/>
+      <c r="F111" s="9"/>
+      <c r="G111" s="9"/>
+      <c r="H111" s="9"/>
       <c r="I111" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3554,20 +3581,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K111" s="16"/>
-      <c r="L111" s="16"/>
-      <c r="M111" s="16"/>
-      <c r="N111" s="17"/>
+      <c r="K111" s="11"/>
+      <c r="L111" s="11"/>
+      <c r="M111" s="11"/>
+      <c r="N111" s="12"/>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A112" s="13"/>
-      <c r="B112" s="14"/>
-      <c r="C112" s="14"/>
-      <c r="D112" s="14"/>
-      <c r="E112" s="14"/>
-      <c r="F112" s="14"/>
-      <c r="G112" s="14"/>
-      <c r="H112" s="14"/>
+      <c r="A112" s="8"/>
+      <c r="B112" s="9"/>
+      <c r="C112" s="9"/>
+      <c r="D112" s="9"/>
+      <c r="E112" s="9"/>
+      <c r="F112" s="9"/>
+      <c r="G112" s="9"/>
+      <c r="H112" s="9"/>
       <c r="I112" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3576,20 +3603,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K112" s="16"/>
-      <c r="L112" s="16"/>
-      <c r="M112" s="16"/>
-      <c r="N112" s="17"/>
+      <c r="K112" s="11"/>
+      <c r="L112" s="11"/>
+      <c r="M112" s="11"/>
+      <c r="N112" s="12"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A113" s="13"/>
-      <c r="B113" s="14"/>
-      <c r="C113" s="14"/>
-      <c r="D113" s="14"/>
-      <c r="E113" s="14"/>
-      <c r="F113" s="14"/>
-      <c r="G113" s="14"/>
-      <c r="H113" s="14"/>
+      <c r="A113" s="8"/>
+      <c r="B113" s="9"/>
+      <c r="C113" s="9"/>
+      <c r="D113" s="9"/>
+      <c r="E113" s="9"/>
+      <c r="F113" s="9"/>
+      <c r="G113" s="9"/>
+      <c r="H113" s="9"/>
       <c r="I113" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3598,20 +3625,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K113" s="16"/>
-      <c r="L113" s="16"/>
-      <c r="M113" s="16"/>
-      <c r="N113" s="17"/>
+      <c r="K113" s="11"/>
+      <c r="L113" s="11"/>
+      <c r="M113" s="11"/>
+      <c r="N113" s="12"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A114" s="13"/>
-      <c r="B114" s="14"/>
-      <c r="C114" s="14"/>
-      <c r="D114" s="14"/>
-      <c r="E114" s="14"/>
-      <c r="F114" s="14"/>
-      <c r="G114" s="14"/>
-      <c r="H114" s="14"/>
+      <c r="A114" s="8"/>
+      <c r="B114" s="9"/>
+      <c r="C114" s="9"/>
+      <c r="D114" s="9"/>
+      <c r="E114" s="9"/>
+      <c r="F114" s="9"/>
+      <c r="G114" s="9"/>
+      <c r="H114" s="9"/>
       <c r="I114" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3620,20 +3647,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K114" s="16"/>
-      <c r="L114" s="16"/>
-      <c r="M114" s="16"/>
-      <c r="N114" s="17"/>
+      <c r="K114" s="11"/>
+      <c r="L114" s="11"/>
+      <c r="M114" s="11"/>
+      <c r="N114" s="12"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A115" s="13"/>
-      <c r="B115" s="14"/>
-      <c r="C115" s="14"/>
-      <c r="D115" s="14"/>
-      <c r="E115" s="14"/>
-      <c r="F115" s="14"/>
-      <c r="G115" s="14"/>
-      <c r="H115" s="14"/>
+      <c r="A115" s="8"/>
+      <c r="B115" s="9"/>
+      <c r="C115" s="9"/>
+      <c r="D115" s="9"/>
+      <c r="E115" s="9"/>
+      <c r="F115" s="9"/>
+      <c r="G115" s="9"/>
+      <c r="H115" s="9"/>
       <c r="I115" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3642,20 +3669,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K115" s="16"/>
-      <c r="L115" s="16"/>
-      <c r="M115" s="16"/>
-      <c r="N115" s="17"/>
+      <c r="K115" s="11"/>
+      <c r="L115" s="11"/>
+      <c r="M115" s="11"/>
+      <c r="N115" s="12"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A116" s="13"/>
-      <c r="B116" s="14"/>
-      <c r="C116" s="14"/>
-      <c r="D116" s="14"/>
-      <c r="E116" s="14"/>
-      <c r="F116" s="14"/>
-      <c r="G116" s="14"/>
-      <c r="H116" s="14"/>
+      <c r="A116" s="8"/>
+      <c r="B116" s="9"/>
+      <c r="C116" s="9"/>
+      <c r="D116" s="9"/>
+      <c r="E116" s="9"/>
+      <c r="F116" s="9"/>
+      <c r="G116" s="9"/>
+      <c r="H116" s="9"/>
       <c r="I116" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3664,20 +3691,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K116" s="16"/>
-      <c r="L116" s="16"/>
-      <c r="M116" s="16"/>
-      <c r="N116" s="17"/>
+      <c r="K116" s="11"/>
+      <c r="L116" s="11"/>
+      <c r="M116" s="11"/>
+      <c r="N116" s="12"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A117" s="13"/>
-      <c r="B117" s="14"/>
-      <c r="C117" s="14"/>
-      <c r="D117" s="14"/>
-      <c r="E117" s="14"/>
-      <c r="F117" s="14"/>
-      <c r="G117" s="14"/>
-      <c r="H117" s="14"/>
+      <c r="A117" s="8"/>
+      <c r="B117" s="9"/>
+      <c r="C117" s="9"/>
+      <c r="D117" s="9"/>
+      <c r="E117" s="9"/>
+      <c r="F117" s="9"/>
+      <c r="G117" s="9"/>
+      <c r="H117" s="9"/>
       <c r="I117" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3686,20 +3713,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K117" s="16"/>
-      <c r="L117" s="16"/>
-      <c r="M117" s="16"/>
-      <c r="N117" s="17"/>
+      <c r="K117" s="11"/>
+      <c r="L117" s="11"/>
+      <c r="M117" s="11"/>
+      <c r="N117" s="12"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A118" s="13"/>
-      <c r="B118" s="14"/>
-      <c r="C118" s="14"/>
-      <c r="D118" s="14"/>
-      <c r="E118" s="14"/>
-      <c r="F118" s="14"/>
-      <c r="G118" s="14"/>
-      <c r="H118" s="14"/>
+      <c r="A118" s="8"/>
+      <c r="B118" s="9"/>
+      <c r="C118" s="9"/>
+      <c r="D118" s="9"/>
+      <c r="E118" s="9"/>
+      <c r="F118" s="9"/>
+      <c r="G118" s="9"/>
+      <c r="H118" s="9"/>
       <c r="I118" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3708,20 +3735,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K118" s="16"/>
-      <c r="L118" s="16"/>
-      <c r="M118" s="16"/>
-      <c r="N118" s="17"/>
+      <c r="K118" s="11"/>
+      <c r="L118" s="11"/>
+      <c r="M118" s="11"/>
+      <c r="N118" s="12"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A119" s="13"/>
-      <c r="B119" s="14"/>
-      <c r="C119" s="14"/>
-      <c r="D119" s="14"/>
-      <c r="E119" s="14"/>
-      <c r="F119" s="14"/>
-      <c r="G119" s="14"/>
-      <c r="H119" s="14"/>
+      <c r="A119" s="8"/>
+      <c r="B119" s="9"/>
+      <c r="C119" s="9"/>
+      <c r="D119" s="9"/>
+      <c r="E119" s="9"/>
+      <c r="F119" s="9"/>
+      <c r="G119" s="9"/>
+      <c r="H119" s="9"/>
       <c r="I119" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3730,20 +3757,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K119" s="16"/>
-      <c r="L119" s="16"/>
-      <c r="M119" s="16"/>
-      <c r="N119" s="17"/>
+      <c r="K119" s="11"/>
+      <c r="L119" s="11"/>
+      <c r="M119" s="11"/>
+      <c r="N119" s="12"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A120" s="13"/>
-      <c r="B120" s="14"/>
-      <c r="C120" s="14"/>
-      <c r="D120" s="14"/>
-      <c r="E120" s="14"/>
-      <c r="F120" s="14"/>
-      <c r="G120" s="14"/>
-      <c r="H120" s="14"/>
+      <c r="A120" s="8"/>
+      <c r="B120" s="9"/>
+      <c r="C120" s="9"/>
+      <c r="D120" s="9"/>
+      <c r="E120" s="9"/>
+      <c r="F120" s="9"/>
+      <c r="G120" s="9"/>
+      <c r="H120" s="9"/>
       <c r="I120" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3752,20 +3779,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K120" s="16"/>
-      <c r="L120" s="16"/>
-      <c r="M120" s="16"/>
-      <c r="N120" s="17"/>
+      <c r="K120" s="11"/>
+      <c r="L120" s="11"/>
+      <c r="M120" s="11"/>
+      <c r="N120" s="12"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A121" s="13"/>
-      <c r="B121" s="14"/>
-      <c r="C121" s="14"/>
-      <c r="D121" s="14"/>
-      <c r="E121" s="14"/>
-      <c r="F121" s="14"/>
-      <c r="G121" s="14"/>
-      <c r="H121" s="14"/>
+      <c r="A121" s="8"/>
+      <c r="B121" s="9"/>
+      <c r="C121" s="9"/>
+      <c r="D121" s="9"/>
+      <c r="E121" s="9"/>
+      <c r="F121" s="9"/>
+      <c r="G121" s="9"/>
+      <c r="H121" s="9"/>
       <c r="I121" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3774,20 +3801,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K121" s="16"/>
-      <c r="L121" s="16"/>
-      <c r="M121" s="16"/>
-      <c r="N121" s="17"/>
+      <c r="K121" s="11"/>
+      <c r="L121" s="11"/>
+      <c r="M121" s="11"/>
+      <c r="N121" s="12"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A122" s="13"/>
-      <c r="B122" s="14"/>
-      <c r="C122" s="14"/>
-      <c r="D122" s="14"/>
-      <c r="E122" s="14"/>
-      <c r="F122" s="14"/>
-      <c r="G122" s="14"/>
-      <c r="H122" s="14"/>
+      <c r="A122" s="8"/>
+      <c r="B122" s="9"/>
+      <c r="C122" s="9"/>
+      <c r="D122" s="9"/>
+      <c r="E122" s="9"/>
+      <c r="F122" s="9"/>
+      <c r="G122" s="9"/>
+      <c r="H122" s="9"/>
       <c r="I122" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3796,20 +3823,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K122" s="16"/>
-      <c r="L122" s="16"/>
-      <c r="M122" s="16"/>
-      <c r="N122" s="17"/>
+      <c r="K122" s="11"/>
+      <c r="L122" s="11"/>
+      <c r="M122" s="11"/>
+      <c r="N122" s="12"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A123" s="13"/>
-      <c r="B123" s="14"/>
-      <c r="C123" s="14"/>
-      <c r="D123" s="14"/>
-      <c r="E123" s="14"/>
-      <c r="F123" s="14"/>
-      <c r="G123" s="14"/>
-      <c r="H123" s="14"/>
+      <c r="A123" s="8"/>
+      <c r="B123" s="9"/>
+      <c r="C123" s="9"/>
+      <c r="D123" s="9"/>
+      <c r="E123" s="9"/>
+      <c r="F123" s="9"/>
+      <c r="G123" s="9"/>
+      <c r="H123" s="9"/>
       <c r="I123" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3818,20 +3845,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K123" s="16"/>
-      <c r="L123" s="16"/>
-      <c r="M123" s="16"/>
-      <c r="N123" s="17"/>
+      <c r="K123" s="11"/>
+      <c r="L123" s="11"/>
+      <c r="M123" s="11"/>
+      <c r="N123" s="12"/>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A124" s="13"/>
-      <c r="B124" s="14"/>
-      <c r="C124" s="14"/>
-      <c r="D124" s="14"/>
-      <c r="E124" s="14"/>
-      <c r="F124" s="14"/>
-      <c r="G124" s="14"/>
-      <c r="H124" s="14"/>
+      <c r="A124" s="8"/>
+      <c r="B124" s="9"/>
+      <c r="C124" s="9"/>
+      <c r="D124" s="9"/>
+      <c r="E124" s="9"/>
+      <c r="F124" s="9"/>
+      <c r="G124" s="9"/>
+      <c r="H124" s="9"/>
       <c r="I124" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3840,20 +3867,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K124" s="16"/>
-      <c r="L124" s="16"/>
-      <c r="M124" s="16"/>
-      <c r="N124" s="17"/>
+      <c r="K124" s="11"/>
+      <c r="L124" s="11"/>
+      <c r="M124" s="11"/>
+      <c r="N124" s="12"/>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A125" s="13"/>
-      <c r="B125" s="14"/>
-      <c r="C125" s="14"/>
-      <c r="D125" s="14"/>
-      <c r="E125" s="14"/>
-      <c r="F125" s="14"/>
-      <c r="G125" s="14"/>
-      <c r="H125" s="14"/>
+      <c r="A125" s="8"/>
+      <c r="B125" s="9"/>
+      <c r="C125" s="9"/>
+      <c r="D125" s="9"/>
+      <c r="E125" s="9"/>
+      <c r="F125" s="9"/>
+      <c r="G125" s="9"/>
+      <c r="H125" s="9"/>
       <c r="I125" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3862,20 +3889,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K125" s="16"/>
-      <c r="L125" s="16"/>
-      <c r="M125" s="16"/>
-      <c r="N125" s="17"/>
+      <c r="K125" s="11"/>
+      <c r="L125" s="11"/>
+      <c r="M125" s="11"/>
+      <c r="N125" s="12"/>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A126" s="13"/>
-      <c r="B126" s="14"/>
-      <c r="C126" s="14"/>
-      <c r="D126" s="14"/>
-      <c r="E126" s="14"/>
-      <c r="F126" s="14"/>
-      <c r="G126" s="14"/>
-      <c r="H126" s="14"/>
+      <c r="A126" s="8"/>
+      <c r="B126" s="9"/>
+      <c r="C126" s="9"/>
+      <c r="D126" s="9"/>
+      <c r="E126" s="9"/>
+      <c r="F126" s="9"/>
+      <c r="G126" s="9"/>
+      <c r="H126" s="9"/>
       <c r="I126" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3884,20 +3911,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K126" s="16"/>
-      <c r="L126" s="16"/>
-      <c r="M126" s="16"/>
-      <c r="N126" s="17"/>
+      <c r="K126" s="11"/>
+      <c r="L126" s="11"/>
+      <c r="M126" s="11"/>
+      <c r="N126" s="12"/>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A127" s="13"/>
-      <c r="B127" s="14"/>
-      <c r="C127" s="14"/>
-      <c r="D127" s="14"/>
-      <c r="E127" s="14"/>
-      <c r="F127" s="14"/>
-      <c r="G127" s="14"/>
-      <c r="H127" s="14"/>
+      <c r="A127" s="8"/>
+      <c r="B127" s="9"/>
+      <c r="C127" s="9"/>
+      <c r="D127" s="9"/>
+      <c r="E127" s="9"/>
+      <c r="F127" s="9"/>
+      <c r="G127" s="9"/>
+      <c r="H127" s="9"/>
       <c r="I127" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3906,20 +3933,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K127" s="16"/>
-      <c r="L127" s="16"/>
-      <c r="M127" s="16"/>
-      <c r="N127" s="17"/>
+      <c r="K127" s="11"/>
+      <c r="L127" s="11"/>
+      <c r="M127" s="11"/>
+      <c r="N127" s="12"/>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A128" s="13"/>
-      <c r="B128" s="14"/>
-      <c r="C128" s="14"/>
-      <c r="D128" s="14"/>
-      <c r="E128" s="14"/>
-      <c r="F128" s="14"/>
-      <c r="G128" s="14"/>
-      <c r="H128" s="14"/>
+      <c r="A128" s="8"/>
+      <c r="B128" s="9"/>
+      <c r="C128" s="9"/>
+      <c r="D128" s="9"/>
+      <c r="E128" s="9"/>
+      <c r="F128" s="9"/>
+      <c r="G128" s="9"/>
+      <c r="H128" s="9"/>
       <c r="I128" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3928,20 +3955,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K128" s="16"/>
-      <c r="L128" s="16"/>
-      <c r="M128" s="16"/>
-      <c r="N128" s="17"/>
+      <c r="K128" s="11"/>
+      <c r="L128" s="11"/>
+      <c r="M128" s="11"/>
+      <c r="N128" s="12"/>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A129" s="13"/>
-      <c r="B129" s="14"/>
-      <c r="C129" s="14"/>
-      <c r="D129" s="14"/>
-      <c r="E129" s="14"/>
-      <c r="F129" s="14"/>
-      <c r="G129" s="14"/>
-      <c r="H129" s="14"/>
+      <c r="A129" s="8"/>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="9"/>
+      <c r="E129" s="9"/>
+      <c r="F129" s="9"/>
+      <c r="G129" s="9"/>
+      <c r="H129" s="9"/>
       <c r="I129" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3950,20 +3977,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K129" s="16"/>
-      <c r="L129" s="16"/>
-      <c r="M129" s="16"/>
-      <c r="N129" s="17"/>
+      <c r="K129" s="11"/>
+      <c r="L129" s="11"/>
+      <c r="M129" s="11"/>
+      <c r="N129" s="12"/>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A130" s="13"/>
-      <c r="B130" s="14"/>
-      <c r="C130" s="14"/>
-      <c r="D130" s="14"/>
-      <c r="E130" s="14"/>
-      <c r="F130" s="14"/>
-      <c r="G130" s="14"/>
-      <c r="H130" s="14"/>
+      <c r="A130" s="8"/>
+      <c r="B130" s="9"/>
+      <c r="C130" s="9"/>
+      <c r="D130" s="9"/>
+      <c r="E130" s="9"/>
+      <c r="F130" s="9"/>
+      <c r="G130" s="9"/>
+      <c r="H130" s="9"/>
       <c r="I130" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3972,20 +3999,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K130" s="16"/>
-      <c r="L130" s="16"/>
-      <c r="M130" s="16"/>
-      <c r="N130" s="17"/>
+      <c r="K130" s="11"/>
+      <c r="L130" s="11"/>
+      <c r="M130" s="11"/>
+      <c r="N130" s="12"/>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A131" s="13"/>
-      <c r="B131" s="14"/>
-      <c r="C131" s="14"/>
-      <c r="D131" s="14"/>
-      <c r="E131" s="14"/>
-      <c r="F131" s="14"/>
-      <c r="G131" s="14"/>
-      <c r="H131" s="14"/>
+      <c r="A131" s="8"/>
+      <c r="B131" s="9"/>
+      <c r="C131" s="9"/>
+      <c r="D131" s="9"/>
+      <c r="E131" s="9"/>
+      <c r="F131" s="9"/>
+      <c r="G131" s="9"/>
+      <c r="H131" s="9"/>
       <c r="I131" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3994,20 +4021,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K131" s="16"/>
-      <c r="L131" s="16"/>
-      <c r="M131" s="16"/>
-      <c r="N131" s="17"/>
+      <c r="K131" s="11"/>
+      <c r="L131" s="11"/>
+      <c r="M131" s="11"/>
+      <c r="N131" s="12"/>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A132" s="13"/>
-      <c r="B132" s="14"/>
-      <c r="C132" s="14"/>
-      <c r="D132" s="14"/>
-      <c r="E132" s="14"/>
-      <c r="F132" s="14"/>
-      <c r="G132" s="14"/>
-      <c r="H132" s="14"/>
+      <c r="A132" s="8"/>
+      <c r="B132" s="9"/>
+      <c r="C132" s="9"/>
+      <c r="D132" s="9"/>
+      <c r="E132" s="9"/>
+      <c r="F132" s="9"/>
+      <c r="G132" s="9"/>
+      <c r="H132" s="9"/>
       <c r="I132" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4016,20 +4043,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K132" s="16"/>
-      <c r="L132" s="16"/>
-      <c r="M132" s="16"/>
-      <c r="N132" s="17"/>
+      <c r="K132" s="11"/>
+      <c r="L132" s="11"/>
+      <c r="M132" s="11"/>
+      <c r="N132" s="12"/>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A133" s="13"/>
-      <c r="B133" s="14"/>
-      <c r="C133" s="14"/>
-      <c r="D133" s="14"/>
-      <c r="E133" s="14"/>
-      <c r="F133" s="14"/>
-      <c r="G133" s="14"/>
-      <c r="H133" s="14"/>
+      <c r="A133" s="8"/>
+      <c r="B133" s="9"/>
+      <c r="C133" s="9"/>
+      <c r="D133" s="9"/>
+      <c r="E133" s="9"/>
+      <c r="F133" s="9"/>
+      <c r="G133" s="9"/>
+      <c r="H133" s="9"/>
       <c r="I133" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4038,20 +4065,20 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K133" s="16"/>
-      <c r="L133" s="16"/>
-      <c r="M133" s="16"/>
-      <c r="N133" s="17"/>
+      <c r="K133" s="11"/>
+      <c r="L133" s="11"/>
+      <c r="M133" s="11"/>
+      <c r="N133" s="12"/>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A134" s="13"/>
-      <c r="B134" s="14"/>
-      <c r="C134" s="14"/>
-      <c r="D134" s="14"/>
-      <c r="E134" s="14"/>
-      <c r="F134" s="14"/>
-      <c r="G134" s="14"/>
-      <c r="H134" s="14"/>
+      <c r="A134" s="8"/>
+      <c r="B134" s="9"/>
+      <c r="C134" s="9"/>
+      <c r="D134" s="9"/>
+      <c r="E134" s="9"/>
+      <c r="F134" s="9"/>
+      <c r="G134" s="9"/>
+      <c r="H134" s="9"/>
       <c r="I134" s="15" t="str">
         <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
@@ -4060,20 +4087,20 @@
         <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
-      <c r="K134" s="16"/>
-      <c r="L134" s="16"/>
-      <c r="M134" s="16"/>
-      <c r="N134" s="17"/>
+      <c r="K134" s="11"/>
+      <c r="L134" s="11"/>
+      <c r="M134" s="11"/>
+      <c r="N134" s="12"/>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A135" s="13"/>
-      <c r="B135" s="14"/>
-      <c r="C135" s="14"/>
-      <c r="D135" s="14"/>
-      <c r="E135" s="14"/>
-      <c r="F135" s="14"/>
-      <c r="G135" s="14"/>
-      <c r="H135" s="14"/>
+      <c r="A135" s="8"/>
+      <c r="B135" s="9"/>
+      <c r="C135" s="9"/>
+      <c r="D135" s="9"/>
+      <c r="E135" s="9"/>
+      <c r="F135" s="9"/>
+      <c r="G135" s="9"/>
+      <c r="H135" s="9"/>
       <c r="I135" s="15" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4082,20 +4109,20 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="K135" s="16"/>
-      <c r="L135" s="16"/>
-      <c r="M135" s="16"/>
-      <c r="N135" s="17"/>
+      <c r="K135" s="11"/>
+      <c r="L135" s="11"/>
+      <c r="M135" s="11"/>
+      <c r="N135" s="12"/>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A136" s="13"/>
+      <c r="A136" s="8"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
       <c r="D136" s="14"/>
       <c r="E136" s="14"/>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
-      <c r="H136" s="14"/>
+      <c r="H136" s="9"/>
       <c r="I136" s="15" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4104,13 +4131,13 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="K136" s="16"/>
-      <c r="L136" s="16"/>
-      <c r="M136" s="16"/>
-      <c r="N136" s="17"/>
+      <c r="K136" s="11"/>
+      <c r="L136" s="11"/>
+      <c r="M136" s="11"/>
+      <c r="N136" s="12"/>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A137" s="13"/>
+      <c r="A137" s="8"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
       <c r="D137" s="14"/>
@@ -4132,7 +4159,7 @@
       <c r="N137" s="17"/>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A138" s="13"/>
+      <c r="A138" s="8"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
       <c r="D138" s="14"/>
@@ -4154,7 +4181,7 @@
       <c r="N138" s="17"/>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A139" s="13"/>
+      <c r="A139" s="8"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
       <c r="D139" s="14"/>
@@ -4176,7 +4203,7 @@
       <c r="N139" s="17"/>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A140" s="13"/>
+      <c r="A140" s="8"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
       <c r="D140" s="14"/>
@@ -4198,7 +4225,7 @@
       <c r="N140" s="17"/>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A141" s="13"/>
+      <c r="A141" s="8"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
       <c r="D141" s="14"/>
@@ -4220,7 +4247,7 @@
       <c r="N141" s="17"/>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A142" s="13"/>
+      <c r="A142" s="8"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
       <c r="D142" s="14"/>
@@ -4242,7 +4269,7 @@
       <c r="N142" s="17"/>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A143" s="13"/>
+      <c r="A143" s="8"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
       <c r="D143" s="14"/>
@@ -4264,7 +4291,7 @@
       <c r="N143" s="17"/>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A144" s="13"/>
+      <c r="A144" s="8"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
       <c r="D144" s="14"/>
@@ -4286,7 +4313,7 @@
       <c r="N144" s="17"/>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A145" s="13"/>
+      <c r="A145" s="8"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
       <c r="D145" s="14"/>
@@ -4308,7 +4335,7 @@
       <c r="N145" s="17"/>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A146" s="13"/>
+      <c r="A146" s="8"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
       <c r="D146" s="14"/>
@@ -4330,7 +4357,7 @@
       <c r="N146" s="17"/>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A147" s="13"/>
+      <c r="A147" s="8"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
       <c r="D147" s="14"/>
@@ -4352,7 +4379,7 @@
       <c r="N147" s="17"/>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A148" s="13"/>
+      <c r="A148" s="8"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
       <c r="D148" s="14"/>
@@ -4374,7 +4401,7 @@
       <c r="N148" s="17"/>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A149" s="13"/>
+      <c r="A149" s="8"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
       <c r="D149" s="14"/>
@@ -4396,7 +4423,7 @@
       <c r="N149" s="17"/>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A150" s="13"/>
+      <c r="A150" s="8"/>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
       <c r="D150" s="14"/>
@@ -4418,7 +4445,7 @@
       <c r="N150" s="17"/>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A151" s="13"/>
+      <c r="A151" s="8"/>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
       <c r="D151" s="14"/>
@@ -4440,7 +4467,7 @@
       <c r="N151" s="17"/>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A152" s="13"/>
+      <c r="A152" s="8"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
       <c r="D152" s="14"/>
@@ -4462,7 +4489,7 @@
       <c r="N152" s="17"/>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A153" s="13"/>
+      <c r="A153" s="8"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
       <c r="D153" s="14"/>
@@ -4484,7 +4511,7 @@
       <c r="N153" s="17"/>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A154" s="13"/>
+      <c r="A154" s="8"/>
       <c r="B154" s="14"/>
       <c r="C154" s="14"/>
       <c r="D154" s="14"/>
@@ -4506,7 +4533,7 @@
       <c r="N154" s="17"/>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A155" s="13"/>
+      <c r="A155" s="8"/>
       <c r="B155" s="14"/>
       <c r="C155" s="14"/>
       <c r="D155" s="14"/>
@@ -4528,7 +4555,7 @@
       <c r="N155" s="17"/>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A156" s="13"/>
+      <c r="A156" s="8"/>
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
       <c r="D156" s="14"/>
@@ -4550,7 +4577,7 @@
       <c r="N156" s="17"/>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A157" s="13"/>
+      <c r="A157" s="8"/>
       <c r="B157" s="14"/>
       <c r="C157" s="14"/>
       <c r="D157" s="14"/>
@@ -4572,7 +4599,7 @@
       <c r="N157" s="17"/>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A158" s="13"/>
+      <c r="A158" s="8"/>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
       <c r="D158" s="14"/>
@@ -4594,7 +4621,7 @@
       <c r="N158" s="17"/>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A159" s="13"/>
+      <c r="A159" s="8"/>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
       <c r="D159" s="14"/>
@@ -4616,7 +4643,7 @@
       <c r="N159" s="17"/>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A160" s="13"/>
+      <c r="A160" s="8"/>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
       <c r="D160" s="14"/>
@@ -4638,7 +4665,7 @@
       <c r="N160" s="17"/>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A161" s="13"/>
+      <c r="A161" s="8"/>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
       <c r="D161" s="14"/>
@@ -4660,7 +4687,7 @@
       <c r="N161" s="17"/>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A162" s="13"/>
+      <c r="A162" s="8"/>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
       <c r="D162" s="14"/>
@@ -4682,7 +4709,7 @@
       <c r="N162" s="17"/>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A163" s="13"/>
+      <c r="A163" s="8"/>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
       <c r="D163" s="14"/>
@@ -4704,7 +4731,7 @@
       <c r="N163" s="17"/>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A164" s="13"/>
+      <c r="A164" s="8"/>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
       <c r="D164" s="14"/>
@@ -4726,7 +4753,7 @@
       <c r="N164" s="17"/>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A165" s="13"/>
+      <c r="A165" s="8"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
       <c r="D165" s="14"/>
@@ -4748,7 +4775,7 @@
       <c r="N165" s="17"/>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A166" s="13"/>
+      <c r="A166" s="8"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14"/>
       <c r="D166" s="14"/>
@@ -4770,7 +4797,7 @@
       <c r="N166" s="17"/>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A167" s="13"/>
+      <c r="A167" s="8"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
       <c r="D167" s="14"/>
@@ -4792,7 +4819,7 @@
       <c r="N167" s="17"/>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A168" s="13"/>
+      <c r="A168" s="8"/>
       <c r="B168" s="14"/>
       <c r="C168" s="14"/>
       <c r="D168" s="14"/>
@@ -4814,7 +4841,7 @@
       <c r="N168" s="17"/>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A169" s="13"/>
+      <c r="A169" s="8"/>
       <c r="B169" s="14"/>
       <c r="C169" s="14"/>
       <c r="D169" s="14"/>
@@ -4836,7 +4863,7 @@
       <c r="N169" s="17"/>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A170" s="13"/>
+      <c r="A170" s="8"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
       <c r="D170" s="14"/>
@@ -4858,7 +4885,7 @@
       <c r="N170" s="17"/>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A171" s="13"/>
+      <c r="A171" s="8"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
       <c r="D171" s="14"/>
@@ -4880,7 +4907,7 @@
       <c r="N171" s="17"/>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A172" s="13"/>
+      <c r="A172" s="8"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
       <c r="D172" s="14"/>
@@ -4902,7 +4929,7 @@
       <c r="N172" s="17"/>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A173" s="13"/>
+      <c r="A173" s="8"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
       <c r="D173" s="14"/>
@@ -4924,7 +4951,7 @@
       <c r="N173" s="17"/>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A174" s="13"/>
+      <c r="A174" s="8"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
       <c r="D174" s="14"/>
@@ -4946,7 +4973,7 @@
       <c r="N174" s="17"/>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A175" s="13"/>
+      <c r="A175" s="8"/>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
       <c r="D175" s="14"/>
@@ -4968,7 +4995,7 @@
       <c r="N175" s="17"/>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A176" s="13"/>
+      <c r="A176" s="8"/>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
       <c r="D176" s="14"/>
@@ -4990,7 +5017,7 @@
       <c r="N176" s="17"/>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A177" s="13"/>
+      <c r="A177" s="8"/>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
       <c r="D177" s="14"/>
@@ -5012,7 +5039,7 @@
       <c r="N177" s="17"/>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A178" s="13"/>
+      <c r="A178" s="8"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
       <c r="D178" s="14"/>
@@ -5034,7 +5061,7 @@
       <c r="N178" s="17"/>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A179" s="13"/>
+      <c r="A179" s="8"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
       <c r="D179" s="14"/>
@@ -5056,7 +5083,7 @@
       <c r="N179" s="17"/>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A180" s="13"/>
+      <c r="A180" s="8"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
       <c r="D180" s="14"/>
@@ -5078,7 +5105,7 @@
       <c r="N180" s="17"/>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A181" s="13"/>
+      <c r="A181" s="8"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
       <c r="D181" s="14"/>
@@ -5100,7 +5127,7 @@
       <c r="N181" s="17"/>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A182" s="13"/>
+      <c r="A182" s="8"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
       <c r="D182" s="14"/>
@@ -5122,7 +5149,7 @@
       <c r="N182" s="17"/>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A183" s="13"/>
+      <c r="A183" s="8"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
       <c r="D183" s="14"/>
@@ -5144,7 +5171,7 @@
       <c r="N183" s="17"/>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A184" s="13"/>
+      <c r="A184" s="8"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
       <c r="D184" s="14"/>
@@ -5166,7 +5193,7 @@
       <c r="N184" s="17"/>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A185" s="13"/>
+      <c r="A185" s="8"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
       <c r="D185" s="14"/>
@@ -5188,7 +5215,7 @@
       <c r="N185" s="17"/>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A186" s="13"/>
+      <c r="A186" s="8"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
       <c r="D186" s="14"/>
@@ -5210,7 +5237,7 @@
       <c r="N186" s="17"/>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A187" s="13"/>
+      <c r="A187" s="8"/>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
       <c r="D187" s="14"/>
@@ -5232,7 +5259,7 @@
       <c r="N187" s="17"/>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A188" s="13"/>
+      <c r="A188" s="8"/>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
       <c r="D188" s="14"/>
@@ -5254,7 +5281,7 @@
       <c r="N188" s="17"/>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A189" s="13"/>
+      <c r="A189" s="8"/>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
       <c r="D189" s="14"/>
@@ -5276,7 +5303,7 @@
       <c r="N189" s="17"/>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A190" s="13"/>
+      <c r="A190" s="8"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
       <c r="D190" s="14"/>
@@ -5298,7 +5325,7 @@
       <c r="N190" s="17"/>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A191" s="13"/>
+      <c r="A191" s="8"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
       <c r="D191" s="14"/>
@@ -5320,7 +5347,7 @@
       <c r="N191" s="17"/>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A192" s="13"/>
+      <c r="A192" s="8"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
       <c r="D192" s="14"/>
@@ -5342,7 +5369,7 @@
       <c r="N192" s="17"/>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A193" s="13"/>
+      <c r="A193" s="8"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
       <c r="D193" s="14"/>
@@ -5364,7 +5391,7 @@
       <c r="N193" s="17"/>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A194" s="13"/>
+      <c r="A194" s="8"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
       <c r="D194" s="14"/>
@@ -5386,7 +5413,7 @@
       <c r="N194" s="17"/>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A195" s="13"/>
+      <c r="A195" s="8"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
       <c r="D195" s="14"/>
@@ -5408,7 +5435,7 @@
       <c r="N195" s="17"/>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A196" s="13"/>
+      <c r="A196" s="8"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
       <c r="D196" s="14"/>
@@ -5430,7 +5457,7 @@
       <c r="N196" s="17"/>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A197" s="13"/>
+      <c r="A197" s="8"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
       <c r="D197" s="14"/>
@@ -5452,7 +5479,7 @@
       <c r="N197" s="17"/>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A198" s="13"/>
+      <c r="A198" s="8"/>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
       <c r="D198" s="14"/>
@@ -5474,7 +5501,7 @@
       <c r="N198" s="17"/>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A199" s="13"/>
+      <c r="A199" s="8"/>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
       <c r="D199" s="14"/>
@@ -5496,7 +5523,7 @@
       <c r="N199" s="17"/>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A200" s="13"/>
+      <c r="A200" s="8"/>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
       <c r="D200" s="14"/>
@@ -5518,7 +5545,7 @@
       <c r="N200" s="17"/>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A201" s="13"/>
+      <c r="A201" s="8"/>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
       <c r="D201" s="14"/>
@@ -5540,7 +5567,7 @@
       <c r="N201" s="17"/>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A202" s="13"/>
+      <c r="A202" s="8"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
       <c r="D202" s="14"/>
@@ -5562,7 +5589,7 @@
       <c r="N202" s="17"/>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A203" s="13"/>
+      <c r="A203" s="8"/>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
       <c r="D203" s="14"/>
@@ -5584,7 +5611,7 @@
       <c r="N203" s="17"/>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A204" s="13"/>
+      <c r="A204" s="8"/>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
       <c r="D204" s="14"/>
@@ -5606,7 +5633,7 @@
       <c r="N204" s="17"/>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A205" s="13"/>
+      <c r="A205" s="8"/>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
       <c r="D205" s="14"/>
@@ -5628,7 +5655,7 @@
       <c r="N205" s="17"/>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A206" s="13"/>
+      <c r="A206" s="8"/>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
       <c r="D206" s="14"/>
@@ -5650,7 +5677,7 @@
       <c r="N206" s="17"/>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A207" s="13"/>
+      <c r="A207" s="8"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
       <c r="D207" s="14"/>
@@ -5672,7 +5699,7 @@
       <c r="N207" s="17"/>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A208" s="13"/>
+      <c r="A208" s="8"/>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
       <c r="D208" s="14"/>
@@ -5694,7 +5721,7 @@
       <c r="N208" s="17"/>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A209" s="13"/>
+      <c r="A209" s="8"/>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
       <c r="D209" s="14"/>
@@ -5716,7 +5743,7 @@
       <c r="N209" s="17"/>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A210" s="13"/>
+      <c r="A210" s="8"/>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
       <c r="D210" s="14"/>
@@ -5738,7 +5765,7 @@
       <c r="N210" s="17"/>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A211" s="13"/>
+      <c r="A211" s="8"/>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
       <c r="D211" s="14"/>

--- a/12600717.xlsx
+++ b/12600717.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python CAP776 Excell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D554F22D-AC97-466D-9447-D878E7722FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E6F52B-73F3-44DA-821B-B44C3D453FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -261,6 +261,36 @@
   <si>
     <t>Attended 5 classes; stayed on track with coursework and made solid progress on programming tasks.</t>
   </si>
+  <si>
+    <t>Busy day with 6 classes; stayed attentive and finished daily lab work.</t>
+  </si>
+  <si>
+    <t>Heavy 7-class schedule; completed classes and spent time on coding project.</t>
+  </si>
+  <si>
+    <t>Weekend study routine; made major progress on project implementation.</t>
+  </si>
+  <si>
+    <t>Rest and reset day; caught up on reading and prepared for the week ahead.</t>
+  </si>
+  <si>
+    <t>Attended 5 classes; smooth start to the week with steady study hours.</t>
+  </si>
+  <si>
+    <t>Attended 5 classes; completed practice problems and coding tasks.</t>
+  </si>
+  <si>
+    <t>Balanced day with 4 classes; focused on workout and core subject review.</t>
+  </si>
+  <si>
+    <t>Attended 6 classes; managed homework assignments in the evening.</t>
+  </si>
+  <si>
+    <t>End of the week with 7 classes; wrapped up pending lab write-ups.</t>
+  </si>
+  <si>
+    <t>Lighter lecture schedule completed study goals and evening revision.</t>
+  </si>
 </sst>
 </file>
 
@@ -269,7 +299,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,6 +380,13 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -398,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -442,6 +479,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1452,225 +1492,465 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="15" t="str">
+    <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B15" s="9">
+        <v>420</v>
+      </c>
+      <c r="C15" s="9">
+        <v>45</v>
+      </c>
+      <c r="D15" s="9">
+        <v>120</v>
+      </c>
+      <c r="E15" s="9">
+        <v>90</v>
+      </c>
+      <c r="F15" s="9">
+        <v>200</v>
+      </c>
+      <c r="G15" s="9">
+        <v>4</v>
+      </c>
+      <c r="H15" s="9">
+        <v>180</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1055</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="12"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="15" t="str">
+        <v>385</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B16" s="9">
+        <v>450</v>
+      </c>
+      <c r="C16" s="9">
+        <v>30</v>
+      </c>
+      <c r="D16" s="9">
+        <v>150</v>
+      </c>
+      <c r="E16" s="9">
+        <v>90</v>
+      </c>
+      <c r="F16" s="9">
+        <v>300</v>
+      </c>
+      <c r="G16" s="9">
+        <v>6</v>
+      </c>
+      <c r="H16" s="9">
+        <v>150</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="12"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="15" t="str">
+        <v>270</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B17" s="9">
+        <v>420</v>
+      </c>
+      <c r="C17" s="9">
+        <v>30</v>
+      </c>
+      <c r="D17" s="9">
+        <v>90</v>
+      </c>
+      <c r="E17" s="9">
+        <v>120</v>
+      </c>
+      <c r="F17" s="9">
+        <v>350</v>
+      </c>
+      <c r="G17" s="9">
+        <v>7</v>
+      </c>
+      <c r="H17" s="9">
+        <v>180</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="12"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="15" t="str">
+        <v>250</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B18" s="9">
+        <v>510</v>
+      </c>
+      <c r="C18" s="9">
+        <v>60</v>
+      </c>
+      <c r="D18" s="9">
+        <v>180</v>
+      </c>
+      <c r="E18" s="9">
+        <v>150</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>240</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="12"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="15" t="str">
+        <v>300</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B19" s="9">
+        <v>480</v>
+      </c>
+      <c r="C19" s="9">
+        <v>45</v>
+      </c>
+      <c r="D19" s="9">
+        <v>150</v>
+      </c>
+      <c r="E19" s="9">
+        <v>120</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9">
+        <v>300</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1095</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="12"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="15" t="str">
+        <v>345</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B20" s="9">
+        <v>420</v>
+      </c>
+      <c r="C20" s="9">
+        <v>45</v>
+      </c>
+      <c r="D20" s="9">
+        <v>120</v>
+      </c>
+      <c r="E20" s="9">
+        <v>90</v>
+      </c>
+      <c r="F20" s="9">
+        <v>250</v>
+      </c>
+      <c r="G20" s="9">
+        <v>5</v>
+      </c>
+      <c r="H20" s="9">
+        <v>180</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1105</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="12"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="15" t="str">
+        <v>335</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B21" s="9">
+        <v>450</v>
+      </c>
+      <c r="C21" s="9">
+        <v>30</v>
+      </c>
+      <c r="D21" s="9">
+        <v>150</v>
+      </c>
+      <c r="E21" s="9">
+        <v>120</v>
+      </c>
+      <c r="F21" s="9">
+        <v>250</v>
+      </c>
+      <c r="G21" s="9">
+        <v>5</v>
+      </c>
+      <c r="H21" s="9">
+        <v>150</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="12"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="15" t="str">
+        <v>290</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B22" s="9">
+        <v>420</v>
+      </c>
+      <c r="C22" s="9">
+        <v>60</v>
+      </c>
+      <c r="D22" s="9">
+        <v>120</v>
+      </c>
+      <c r="E22" s="9">
+        <v>90</v>
+      </c>
+      <c r="F22" s="9">
+        <v>200</v>
+      </c>
+      <c r="G22" s="9">
+        <v>4</v>
+      </c>
+      <c r="H22" s="9">
+        <v>180</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="12"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="15" t="str">
+        <v>370</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B23" s="9">
+        <v>450</v>
+      </c>
+      <c r="C23" s="9">
+        <v>30</v>
+      </c>
+      <c r="D23" s="9">
+        <v>120</v>
+      </c>
+      <c r="E23" s="9">
+        <v>90</v>
+      </c>
+      <c r="F23" s="9">
+        <v>300</v>
+      </c>
+      <c r="G23" s="9">
+        <v>6</v>
+      </c>
+      <c r="H23" s="9">
+        <v>180</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="12"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="15" t="str">
+        <v>270</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B24" s="9">
+        <v>420</v>
+      </c>
+      <c r="C24" s="9">
+        <v>30</v>
+      </c>
+      <c r="D24" s="9">
+        <v>90</v>
+      </c>
+      <c r="E24" s="9">
+        <v>120</v>
+      </c>
+      <c r="F24" s="9">
+        <v>350</v>
+      </c>
+      <c r="G24" s="9">
+        <v>7</v>
+      </c>
+      <c r="H24" s="9">
+        <v>180</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="12"/>
+        <v>250</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
@@ -9995,6 +10275,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/12600717.xlsx
+++ b/12600717.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python CAP776 Excell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E6F52B-73F3-44DA-821B-B44C3D453FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52AF1C84-5EAC-411B-A1A7-D6861F911CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -291,6 +291,27 @@
   <si>
     <t>Lighter lecture schedule completed study goals and evening revision.</t>
   </si>
+  <si>
+    <t>Saturday self-study session; devoted significant time to full-stack project building.</t>
+  </si>
+  <si>
+    <t>Sunday rest day; organized study materials and reviewed core concepts.</t>
+  </si>
+  <si>
+    <t>Attended 5 classes; started the week focused with an evening problem-solving session.</t>
+  </si>
+  <si>
+    <t>Attended 5 classes; completed lab work efficiently and made progress on code repo.</t>
+  </si>
+  <si>
+    <t>Lighter 4-class day; balanced fitness workout with evening assignment work.</t>
+  </si>
+  <si>
+    <t>Busy day with 6 classes; stayed focused in lectures and revised evening notes.</t>
+  </si>
+  <si>
+    <t>End of the week with 7 classes; completed weekly deliverables and lab write-ups.</t>
+  </si>
 </sst>
 </file>
 
@@ -476,12 +497,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -965,74 +986,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12600717</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1534,7 +1555,7 @@
       <c r="M15" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N15" s="21" t="s">
+      <c r="N15" s="18" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1952,159 +1973,327 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="15" t="str">
+    <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B25" s="9">
+        <v>510</v>
+      </c>
+      <c r="C25" s="9">
+        <v>60</v>
+      </c>
+      <c r="D25" s="9">
+        <v>180</v>
+      </c>
+      <c r="E25" s="9">
+        <v>150</v>
+      </c>
+      <c r="F25" s="9">
+        <v>0</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
+      </c>
+      <c r="H25" s="9">
+        <v>240</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="12"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="15" t="str">
+        <v>300</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B26" s="9">
+        <v>480</v>
+      </c>
+      <c r="C26" s="9">
+        <v>45</v>
+      </c>
+      <c r="D26" s="9">
+        <v>150</v>
+      </c>
+      <c r="E26" s="9">
+        <v>120</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>300</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1095</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="12"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="15" t="str">
+        <v>345</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B27" s="9">
+        <v>420</v>
+      </c>
+      <c r="C27" s="9">
+        <v>45</v>
+      </c>
+      <c r="D27" s="9">
+        <v>120</v>
+      </c>
+      <c r="E27" s="9">
+        <v>90</v>
+      </c>
+      <c r="F27" s="9">
+        <v>250</v>
+      </c>
+      <c r="G27" s="9">
+        <v>5</v>
+      </c>
+      <c r="H27" s="9">
+        <v>180</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1105</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="12"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="15" t="str">
+        <v>335</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B28" s="9">
+        <v>450</v>
+      </c>
+      <c r="C28" s="9">
+        <v>30</v>
+      </c>
+      <c r="D28" s="9">
+        <v>150</v>
+      </c>
+      <c r="E28" s="9">
+        <v>120</v>
+      </c>
+      <c r="F28" s="9">
+        <v>250</v>
+      </c>
+      <c r="G28" s="9">
+        <v>5</v>
+      </c>
+      <c r="H28" s="9">
+        <v>150</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="12"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="15" t="str">
+        <v>290</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B29" s="9">
+        <v>420</v>
+      </c>
+      <c r="C29" s="9">
+        <v>60</v>
+      </c>
+      <c r="D29" s="9">
+        <v>120</v>
+      </c>
+      <c r="E29" s="9">
+        <v>90</v>
+      </c>
+      <c r="F29" s="9">
+        <v>200</v>
+      </c>
+      <c r="G29" s="9">
+        <v>4</v>
+      </c>
+      <c r="H29" s="9">
+        <v>180</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="12"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="15" t="str">
+        <v>370</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B30" s="9">
+        <v>450</v>
+      </c>
+      <c r="C30" s="9">
+        <v>30</v>
+      </c>
+      <c r="D30" s="9">
+        <v>120</v>
+      </c>
+      <c r="E30" s="9">
+        <v>90</v>
+      </c>
+      <c r="F30" s="9">
+        <v>300</v>
+      </c>
+      <c r="G30" s="9">
+        <v>6</v>
+      </c>
+      <c r="H30" s="9">
+        <v>180</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="12"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="15" t="str">
+        <v>270</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B31" s="9">
+        <v>420</v>
+      </c>
+      <c r="C31" s="9">
+        <v>30</v>
+      </c>
+      <c r="D31" s="9">
+        <v>90</v>
+      </c>
+      <c r="E31" s="9">
+        <v>120</v>
+      </c>
+      <c r="F31" s="9">
+        <v>350</v>
+      </c>
+      <c r="G31" s="9">
+        <v>7</v>
+      </c>
+      <c r="H31" s="9">
+        <v>180</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="12"/>
+        <v>250</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>

--- a/12600717.xlsx
+++ b/12600717.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python CAP776 Excell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65F5DD8-3939-4163-9273-403D013BFBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78537C9F-F46D-4F5D-B4D0-4457E40F5560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -196,12 +196,6 @@
     <t>5. GOOD PRACTICE</t>
   </si>
   <si>
-    <t>Shantanu Chhetri</t>
-  </si>
-  <si>
-    <t>August</t>
-  </si>
-  <si>
     <t>CAP776 / D1P2634</t>
   </si>
   <si>
@@ -365,6 +359,12 @@
   </si>
   <si>
     <t>Sunday break; organized week plan and relaxed.</t>
+  </si>
+  <si>
+    <t>SHANTANU CHHETRI</t>
+  </si>
+  <si>
+    <t>AUGUST | SEPTEMBER</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1059,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -1076,7 +1076,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -1084,7 +1084,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1184,7 +1184,7 @@
         <v>270</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L6" s="10" t="s">
         <v>50</v>
@@ -1193,7 +1193,7 @@
         <v>51</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1230,16 +1230,16 @@
         <v>250</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1276,16 +1276,16 @@
         <v>300</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1322,16 +1322,16 @@
         <v>345</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L9" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1368,16 +1368,16 @@
         <v>335</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L10" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1414,16 +1414,16 @@
         <v>290</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1469,7 +1469,7 @@
         <v>51</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1506,16 +1506,16 @@
         <v>270</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>51</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1552,16 +1552,16 @@
         <v>250</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L14" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1598,16 +1598,16 @@
         <v>300</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1644,16 +1644,16 @@
         <v>345</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L16" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1690,16 +1690,16 @@
         <v>335</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L17" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1736,16 +1736,16 @@
         <v>290</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1791,7 +1791,7 @@
         <v>51</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1828,16 +1828,16 @@
         <v>270</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M20" s="10" t="s">
         <v>51</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1874,16 +1874,16 @@
         <v>250</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L21" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1920,16 +1920,16 @@
         <v>300</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1966,16 +1966,16 @@
         <v>345</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L23" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2012,16 +2012,16 @@
         <v>335</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L24" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2054,20 +2054,20 @@
         <v>1150</v>
       </c>
       <c r="J25" s="14">
-        <f t="shared" ref="J24:J87" si="3">IF(I25="","",1440-I25)</f>
+        <f t="shared" ref="J25:J87" si="3">IF(I25="","",1440-I25)</f>
         <v>290</v>
       </c>
       <c r="K25" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L25" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="L25" s="10" t="s">
-        <v>59</v>
-      </c>
       <c r="M25" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2113,7 +2113,7 @@
         <v>51</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2150,16 +2150,16 @@
         <v>225</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M27" s="10" t="s">
         <v>51</v>
       </c>
       <c r="N27" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2196,16 +2196,16 @@
         <v>160</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L28" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2242,16 +2242,16 @@
         <v>310</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N29" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2288,16 +2288,16 @@
         <v>315</v>
       </c>
       <c r="K30" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L30" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N30" s="11" t="s">
         <v>70</v>
-      </c>
-      <c r="L30" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="M30" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="N30" s="11" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2334,16 +2334,16 @@
         <v>335</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L31" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2380,7 +2380,7 @@
         <v>290</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L32" s="10" t="s">
         <v>50</v>
@@ -2389,7 +2389,7 @@
         <v>51</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2435,7 +2435,7 @@
         <v>51</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2472,7 +2472,7 @@
         <v>270</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L34" s="10" t="s">
         <v>50</v>
@@ -2481,7 +2481,7 @@
         <v>51</v>
       </c>
       <c r="N34" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2518,16 +2518,16 @@
         <v>250</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N35" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2564,16 +2564,16 @@
         <v>300</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M36" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N36" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2610,16 +2610,16 @@
         <v>345</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L37" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M37" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N37" s="11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2656,16 +2656,16 @@
         <v>335</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L38" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M38" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N38" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2702,16 +2702,16 @@
         <v>290</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L39" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M39" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N39" s="11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2757,7 +2757,7 @@
         <v>51</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2794,16 +2794,16 @@
         <v>270</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L41" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M41" s="10" t="s">
         <v>51</v>
       </c>
       <c r="N41" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2840,16 +2840,16 @@
         <v>250</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L42" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M42" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N42" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2886,16 +2886,16 @@
         <v>300</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L43" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M43" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N43" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2932,16 +2932,16 @@
         <v>345</v>
       </c>
       <c r="K44" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L44" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2978,16 +2978,16 @@
         <v>335</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L45" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -3024,16 +3024,16 @@
         <v>290</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L46" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -3079,7 +3079,7 @@
         <v>51</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -3116,16 +3116,16 @@
         <v>270</v>
       </c>
       <c r="K48" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L48" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M48" s="10" t="s">
         <v>51</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -3162,16 +3162,16 @@
         <v>250</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L49" s="10" t="s">
         <v>50</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600717.xlsx
+++ b/12600717.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python CAP776 Excell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78537C9F-F46D-4F5D-B4D0-4457E40F5560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3784CD57-9F51-4A86-B424-85A095B5F66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -307,27 +307,6 @@
     <t>End of the week with 7 classes; completed weekly deliverables and lab write-ups.</t>
   </si>
   <si>
-    <t>Attended 6 classes; reviewed semester syllabus and organized study environment.</t>
-  </si>
-  <si>
-    <t>Heavy 7-class schedule; finished day with brief coding practice.</t>
-  </si>
-  <si>
-    <t>Weekend self-study; focused on full-stack architecture revision.</t>
-  </si>
-  <si>
-    <t>Sunday rest and reset; planned study goals for the upcoming week.</t>
-  </si>
-  <si>
-    <t>Attended 5 classes; productive evening study session.</t>
-  </si>
-  <si>
-    <t>Attended 5 classes; completed lab assignments efficiently.</t>
-  </si>
-  <si>
-    <t>Lighter schedule with 4 classes; focused on workout and course revision.</t>
-  </si>
-  <si>
     <t>Attended 6 classes; completed reading assignments in evening.</t>
   </si>
   <si>
@@ -365,6 +344,27 @@
   </si>
   <si>
     <t>AUGUST | SEPTEMBER</t>
+  </si>
+  <si>
+    <t>Saturday coding deep dive; completed full-stack microservice integration and API endpoints.</t>
+  </si>
+  <si>
+    <t>Sunday rest day; catch-up reading, weekly schedule review, and project planning.</t>
+  </si>
+  <si>
+    <t>Attended 5 classes; productive week start with evening competitive programming practice.</t>
+  </si>
+  <si>
+    <t>Attended 5 classes; finished lab exercises and prepared data science notes.</t>
+  </si>
+  <si>
+    <t>Lighter 4-class schedule; completed workout and revised core database concepts.</t>
+  </si>
+  <si>
+    <t>Attended 6 classes; focused during long lectures and worked on assignment submission.</t>
+  </si>
+  <si>
+    <t>End of academic week with 7 classes; finished weekly project deliverables and lab tasks.</t>
   </si>
 </sst>
 </file>
@@ -1022,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N419"/>
+  <dimension ref="A1:N412"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1059,7 +1059,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -1084,7 +1084,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1150,9 +1150,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>46240</v>
+        <v>46247</v>
       </c>
       <c r="B6" s="9">
         <v>450</v>
@@ -1161,7 +1161,7 @@
         <v>30</v>
       </c>
       <c r="D6" s="9">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E6" s="9">
         <v>90</v>
@@ -1173,21 +1173,21 @@
         <v>6</v>
       </c>
       <c r="H6" s="9">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="I6" s="14">
-        <f t="shared" ref="I6:I21" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I14" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>1170</v>
       </c>
       <c r="J6" s="14">
-        <f t="shared" ref="J6:J24" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J17" si="1">IF(I6="","",1440-I6)</f>
         <v>270</v>
       </c>
       <c r="K6" s="10" t="s">
         <v>56</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M6" s="10" t="s">
         <v>51</v>
@@ -1198,7 +1198,7 @@
     </row>
     <row r="7" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B7" s="9">
         <v>420</v>
@@ -1233,7 +1233,7 @@
         <v>60</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>58</v>
@@ -1244,7 +1244,7 @@
     </row>
     <row r="8" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B8" s="9">
         <v>510</v>
@@ -1288,9 +1288,9 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
-        <v>46243</v>
+        <v>46250</v>
       </c>
       <c r="B9" s="9">
         <v>480</v>
@@ -1334,9 +1334,9 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B10" s="9">
         <v>420</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="11" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="B11" s="9">
         <v>450</v>
@@ -1428,7 +1428,7 @@
     </row>
     <row r="12" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="B12" s="9">
         <v>420</v>
@@ -1472,9 +1472,9 @@
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="B13" s="9">
         <v>450</v>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="14" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B14" s="9">
         <v>420</v>
@@ -1566,7 +1566,7 @@
     </row>
     <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="B15" s="9">
         <v>510</v>
@@ -1590,7 +1590,7 @@
         <v>240</v>
       </c>
       <c r="I15" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I15:I80" si="2">IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
         <v>1140</v>
       </c>
       <c r="J15" s="14">
@@ -1610,9 +1610,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="B16" s="9">
         <v>480</v>
@@ -1636,7 +1636,7 @@
         <v>300</v>
       </c>
       <c r="I16" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1095</v>
       </c>
       <c r="J16" s="14">
@@ -1656,9 +1656,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B17" s="9">
         <v>420</v>
@@ -1682,7 +1682,7 @@
         <v>180</v>
       </c>
       <c r="I17" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1105</v>
       </c>
       <c r="J17" s="14">
@@ -1699,12 +1699,12 @@
         <v>54</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="B18" s="9">
         <v>450</v>
@@ -1728,29 +1728,29 @@
         <v>150</v>
       </c>
       <c r="I18" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1150</v>
       </c>
       <c r="J18" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J18:J80" si="3">IF(I18="","",1440-I18)</f>
         <v>290</v>
       </c>
       <c r="K18" s="10" t="s">
         <v>55</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="M18" s="10" t="s">
         <v>54</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="B19" s="9">
         <v>420</v>
@@ -1759,7 +1759,7 @@
         <v>60</v>
       </c>
       <c r="D19" s="9">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E19" s="9">
         <v>90</v>
@@ -1774,12 +1774,12 @@
         <v>180</v>
       </c>
       <c r="I19" s="14">
-        <f t="shared" si="0"/>
-        <v>1070</v>
+        <f t="shared" si="2"/>
+        <v>1040</v>
       </c>
       <c r="J19" s="14">
-        <f t="shared" si="1"/>
-        <v>370</v>
+        <f t="shared" si="3"/>
+        <v>400</v>
       </c>
       <c r="K19" s="10" t="s">
         <v>49</v>
@@ -1791,24 +1791,24 @@
         <v>51</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="B20" s="9">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="C20" s="9">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D20" s="9">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E20" s="9">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F20" s="9">
         <v>300</v>
@@ -1817,15 +1817,15 @@
         <v>6</v>
       </c>
       <c r="H20" s="9">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I20" s="14">
-        <f t="shared" si="0"/>
-        <v>1170</v>
+        <f t="shared" si="2"/>
+        <v>1215</v>
       </c>
       <c r="J20" s="14">
-        <f t="shared" si="1"/>
-        <v>270</v>
+        <f t="shared" si="3"/>
+        <v>225</v>
       </c>
       <c r="K20" s="10" t="s">
         <v>56</v>
@@ -1837,12 +1837,12 @@
         <v>51</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="B21" s="9">
         <v>420</v>
@@ -1851,10 +1851,10 @@
         <v>30</v>
       </c>
       <c r="D21" s="9">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E21" s="9">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F21" s="9">
         <v>350</v>
@@ -1863,15 +1863,15 @@
         <v>7</v>
       </c>
       <c r="H21" s="9">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I21" s="14">
-        <f t="shared" si="0"/>
-        <v>1190</v>
+        <f t="shared" si="2"/>
+        <v>1280</v>
       </c>
       <c r="J21" s="14">
-        <f t="shared" si="1"/>
-        <v>250</v>
+        <f t="shared" si="3"/>
+        <v>160</v>
       </c>
       <c r="K21" s="10" t="s">
         <v>60</v>
@@ -1883,24 +1883,24 @@
         <v>58</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="B22" s="9">
         <v>510</v>
       </c>
       <c r="C22" s="9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D22" s="9">
+        <v>150</v>
+      </c>
+      <c r="E22" s="9">
         <v>180</v>
-      </c>
-      <c r="E22" s="9">
-        <v>150</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
@@ -1912,38 +1912,38 @@
         <v>240</v>
       </c>
       <c r="I22" s="14">
-        <f t="shared" ref="I22:I87" si="2">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
-        <v>1140</v>
+        <f t="shared" si="2"/>
+        <v>1130</v>
       </c>
       <c r="J22" s="14">
-        <f t="shared" si="1"/>
-        <v>300</v>
+        <f t="shared" si="3"/>
+        <v>310</v>
       </c>
       <c r="K22" s="10" t="s">
         <v>61</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="M22" s="10" t="s">
         <v>54</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="B23" s="9">
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="C23" s="9">
         <v>45</v>
       </c>
       <c r="D23" s="9">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="E23" s="9">
         <v>120</v>
@@ -1955,32 +1955,32 @@
         <v>0</v>
       </c>
       <c r="H23" s="9">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="I23" s="14">
         <f t="shared" si="2"/>
-        <v>1095</v>
+        <v>1125</v>
       </c>
       <c r="J23" s="14">
-        <f t="shared" si="1"/>
-        <v>345</v>
+        <f t="shared" si="3"/>
+        <v>315</v>
       </c>
       <c r="K23" s="10" t="s">
         <v>68</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="M23" s="10" t="s">
         <v>54</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B24" s="9">
         <v>420</v>
@@ -2008,7 +2008,7 @@
         <v>1105</v>
       </c>
       <c r="J24" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>335</v>
       </c>
       <c r="K24" s="10" t="s">
@@ -2021,12 +2021,12 @@
         <v>54</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="B25" s="9">
         <v>450</v>
@@ -2054,34 +2054,34 @@
         <v>1150</v>
       </c>
       <c r="J25" s="14">
-        <f t="shared" ref="J25:J87" si="3">IF(I25="","",1440-I25)</f>
+        <f t="shared" si="3"/>
         <v>290</v>
       </c>
       <c r="K25" s="10" t="s">
         <v>55</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="B26" s="9">
         <v>420</v>
       </c>
       <c r="C26" s="9">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D26" s="9">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E26" s="9">
         <v>90</v>
@@ -2097,11 +2097,11 @@
       </c>
       <c r="I26" s="14">
         <f t="shared" si="2"/>
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="J26" s="14">
         <f t="shared" si="3"/>
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="K26" s="10" t="s">
         <v>49</v>
@@ -2112,25 +2112,25 @@
       <c r="M26" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N26" s="11" t="s">
-        <v>64</v>
+      <c r="N26" s="17" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="B27" s="9">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="C27" s="9">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D27" s="9">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="E27" s="9">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F27" s="9">
         <v>300</v>
@@ -2143,28 +2143,28 @@
       </c>
       <c r="I27" s="14">
         <f t="shared" si="2"/>
-        <v>1215</v>
+        <v>1170</v>
       </c>
       <c r="J27" s="14">
         <f t="shared" si="3"/>
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="K27" s="10" t="s">
         <v>56</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M27" s="10" t="s">
         <v>51</v>
       </c>
       <c r="N27" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B28" s="9">
         <v>420</v>
@@ -2173,10 +2173,10 @@
         <v>30</v>
       </c>
       <c r="D28" s="9">
+        <v>90</v>
+      </c>
+      <c r="E28" s="9">
         <v>120</v>
-      </c>
-      <c r="E28" s="9">
-        <v>150</v>
       </c>
       <c r="F28" s="9">
         <v>350</v>
@@ -2185,44 +2185,44 @@
         <v>7</v>
       </c>
       <c r="H28" s="9">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="I28" s="14">
         <f t="shared" si="2"/>
-        <v>1280</v>
+        <v>1190</v>
       </c>
       <c r="J28" s="14">
         <f t="shared" si="3"/>
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="K28" s="10" t="s">
         <v>60</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M28" s="10" t="s">
         <v>58</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="B29" s="9">
         <v>510</v>
       </c>
       <c r="C29" s="9">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D29" s="9">
+        <v>180</v>
+      </c>
+      <c r="E29" s="9">
         <v>150</v>
-      </c>
-      <c r="E29" s="9">
-        <v>180</v>
       </c>
       <c r="F29" s="9">
         <v>0</v>
@@ -2235,37 +2235,37 @@
       </c>
       <c r="I29" s="14">
         <f t="shared" si="2"/>
-        <v>1130</v>
+        <v>1140</v>
       </c>
       <c r="J29" s="14">
         <f t="shared" si="3"/>
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="K29" s="10" t="s">
         <v>61</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="M29" s="10" t="s">
         <v>54</v>
       </c>
       <c r="N29" s="11" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="B30" s="9">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="C30" s="9">
         <v>45</v>
       </c>
       <c r="D30" s="9">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="E30" s="9">
         <v>120</v>
@@ -2277,32 +2277,32 @@
         <v>0</v>
       </c>
       <c r="H30" s="9">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="I30" s="14">
         <f t="shared" si="2"/>
-        <v>1125</v>
+        <v>1095</v>
       </c>
       <c r="J30" s="14">
         <f t="shared" si="3"/>
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="K30" s="10" t="s">
         <v>68</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="M30" s="10" t="s">
         <v>54</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B31" s="9">
         <v>420</v>
@@ -2343,12 +2343,12 @@
         <v>54</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="B32" s="9">
         <v>450</v>
@@ -2383,24 +2383,24 @@
         <v>55</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="B33" s="9">
         <v>420</v>
       </c>
       <c r="C33" s="9">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D33" s="9">
         <v>120</v>
@@ -2419,11 +2419,11 @@
       </c>
       <c r="I33" s="14">
         <f t="shared" si="2"/>
-        <v>1055</v>
+        <v>1070</v>
       </c>
       <c r="J33" s="14">
         <f t="shared" si="3"/>
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="K33" s="10" t="s">
         <v>49</v>
@@ -2434,13 +2434,13 @@
       <c r="M33" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N33" s="17" t="s">
-        <v>82</v>
+      <c r="N33" s="11" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="B34" s="9">
         <v>450</v>
@@ -2449,7 +2449,7 @@
         <v>30</v>
       </c>
       <c r="D34" s="9">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E34" s="9">
         <v>90</v>
@@ -2461,7 +2461,7 @@
         <v>6</v>
       </c>
       <c r="H34" s="9">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="I34" s="14">
         <f t="shared" si="2"/>
@@ -2475,18 +2475,18 @@
         <v>56</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M34" s="10" t="s">
         <v>51</v>
       </c>
       <c r="N34" s="11" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B35" s="9">
         <v>420</v>
@@ -2521,18 +2521,18 @@
         <v>60</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M35" s="10" t="s">
         <v>58</v>
       </c>
       <c r="N35" s="11" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B36" s="9">
         <v>510</v>
@@ -2573,12 +2573,12 @@
         <v>54</v>
       </c>
       <c r="N36" s="11" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="B37" s="9">
         <v>480</v>
@@ -2619,12 +2619,12 @@
         <v>54</v>
       </c>
       <c r="N37" s="11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="B38" s="9">
         <v>420</v>
@@ -2665,12 +2665,12 @@
         <v>54</v>
       </c>
       <c r="N38" s="11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="B39" s="9">
         <v>450</v>
@@ -2711,12 +2711,12 @@
         <v>54</v>
       </c>
       <c r="N39" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="B40" s="9">
         <v>420</v>
@@ -2757,12 +2757,12 @@
         <v>51</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="B41" s="9">
         <v>450</v>
@@ -2803,12 +2803,12 @@
         <v>51</v>
       </c>
       <c r="N41" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B42" s="9">
         <v>420</v>
@@ -2849,12 +2849,12 @@
         <v>58</v>
       </c>
       <c r="N42" s="11" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B43" s="9">
         <v>510</v>
@@ -2895,12 +2895,12 @@
         <v>54</v>
       </c>
       <c r="N43" s="11" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="B44" s="9">
         <v>480</v>
@@ -2941,12 +2941,12 @@
         <v>54</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B45" s="9">
         <v>420</v>
@@ -2987,12 +2987,12 @@
         <v>54</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="B46" s="9">
         <v>450</v>
@@ -3033,12 +3033,12 @@
         <v>54</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="B47" s="9">
         <v>420</v>
@@ -3079,12 +3079,12 @@
         <v>51</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="B48" s="9">
         <v>450</v>
@@ -3125,12 +3125,12 @@
         <v>51</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="B49" s="9">
         <v>420</v>
@@ -3171,7 +3171,7 @@
         <v>58</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -3866,11 +3866,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I81:I144" si="4">IF(SUM(B81:F81,H81)=0,"",SUM(B81:F81,H81))</f>
         <v/>
       </c>
       <c r="J81" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J81:J144" si="5">IF(I81="","",1440-I81)</f>
         <v/>
       </c>
       <c r="K81" s="10"/>
@@ -3888,11 +3888,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K82" s="10"/>
@@ -3910,11 +3910,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K83" s="10"/>
@@ -3932,11 +3932,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K84" s="10"/>
@@ -3954,11 +3954,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K85" s="10"/>
@@ -3976,11 +3976,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K86" s="10"/>
@@ -3998,11 +3998,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K87" s="10"/>
@@ -4020,11 +4020,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="14" t="str">
-        <f t="shared" ref="I88:I151" si="4">IF(SUM(B88:F88,H88)=0,"",SUM(B88:F88,H88))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="14" t="str">
-        <f t="shared" ref="J88:J151" si="5">IF(I88="","",1440-I88)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K88" s="10"/>
@@ -5274,11 +5274,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I145:I208" si="6">IF(SUM(B145:F145,H145)=0,"",SUM(B145:F145,H145))</f>
         <v/>
       </c>
       <c r="J145" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J145:J208" si="7">IF(I145="","",1440-I145)</f>
         <v/>
       </c>
       <c r="K145" s="10"/>
@@ -5296,11 +5296,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="10"/>
@@ -5310,19 +5310,19 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" s="8"/>
-      <c r="B147" s="9"/>
-      <c r="C147" s="9"/>
-      <c r="D147" s="9"/>
-      <c r="E147" s="9"/>
-      <c r="F147" s="9"/>
-      <c r="G147" s="9"/>
+      <c r="B147" s="13"/>
+      <c r="C147" s="13"/>
+      <c r="D147" s="13"/>
+      <c r="E147" s="13"/>
+      <c r="F147" s="13"/>
+      <c r="G147" s="13"/>
       <c r="H147" s="9"/>
       <c r="I147" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="10"/>
@@ -5332,123 +5332,123 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" s="8"/>
-      <c r="B148" s="9"/>
-      <c r="C148" s="9"/>
-      <c r="D148" s="9"/>
-      <c r="E148" s="9"/>
-      <c r="F148" s="9"/>
-      <c r="G148" s="9"/>
-      <c r="H148" s="9"/>
+      <c r="B148" s="13"/>
+      <c r="C148" s="13"/>
+      <c r="D148" s="13"/>
+      <c r="E148" s="13"/>
+      <c r="F148" s="13"/>
+      <c r="G148" s="13"/>
+      <c r="H148" s="13"/>
       <c r="I148" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K148" s="10"/>
-      <c r="L148" s="10"/>
-      <c r="M148" s="10"/>
-      <c r="N148" s="11"/>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="K148" s="15"/>
+      <c r="L148" s="15"/>
+      <c r="M148" s="15"/>
+      <c r="N148" s="16"/>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" s="8"/>
-      <c r="B149" s="9"/>
-      <c r="C149" s="9"/>
-      <c r="D149" s="9"/>
-      <c r="E149" s="9"/>
-      <c r="F149" s="9"/>
-      <c r="G149" s="9"/>
-      <c r="H149" s="9"/>
+      <c r="B149" s="13"/>
+      <c r="C149" s="13"/>
+      <c r="D149" s="13"/>
+      <c r="E149" s="13"/>
+      <c r="F149" s="13"/>
+      <c r="G149" s="13"/>
+      <c r="H149" s="13"/>
       <c r="I149" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K149" s="10"/>
-      <c r="L149" s="10"/>
-      <c r="M149" s="10"/>
-      <c r="N149" s="11"/>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="K149" s="15"/>
+      <c r="L149" s="15"/>
+      <c r="M149" s="15"/>
+      <c r="N149" s="16"/>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" s="8"/>
-      <c r="B150" s="9"/>
-      <c r="C150" s="9"/>
-      <c r="D150" s="9"/>
-      <c r="E150" s="9"/>
-      <c r="F150" s="9"/>
-      <c r="G150" s="9"/>
-      <c r="H150" s="9"/>
+      <c r="B150" s="13"/>
+      <c r="C150" s="13"/>
+      <c r="D150" s="13"/>
+      <c r="E150" s="13"/>
+      <c r="F150" s="13"/>
+      <c r="G150" s="13"/>
+      <c r="H150" s="13"/>
       <c r="I150" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K150" s="10"/>
-      <c r="L150" s="10"/>
-      <c r="M150" s="10"/>
-      <c r="N150" s="11"/>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="K150" s="15"/>
+      <c r="L150" s="15"/>
+      <c r="M150" s="15"/>
+      <c r="N150" s="16"/>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" s="8"/>
-      <c r="B151" s="9"/>
-      <c r="C151" s="9"/>
-      <c r="D151" s="9"/>
-      <c r="E151" s="9"/>
-      <c r="F151" s="9"/>
-      <c r="G151" s="9"/>
-      <c r="H151" s="9"/>
+      <c r="B151" s="13"/>
+      <c r="C151" s="13"/>
+      <c r="D151" s="13"/>
+      <c r="E151" s="13"/>
+      <c r="F151" s="13"/>
+      <c r="G151" s="13"/>
+      <c r="H151" s="13"/>
       <c r="I151" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K151" s="10"/>
-      <c r="L151" s="10"/>
-      <c r="M151" s="10"/>
-      <c r="N151" s="11"/>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="K151" s="15"/>
+      <c r="L151" s="15"/>
+      <c r="M151" s="15"/>
+      <c r="N151" s="16"/>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" s="8"/>
-      <c r="B152" s="9"/>
-      <c r="C152" s="9"/>
-      <c r="D152" s="9"/>
-      <c r="E152" s="9"/>
-      <c r="F152" s="9"/>
-      <c r="G152" s="9"/>
-      <c r="H152" s="9"/>
+      <c r="B152" s="13"/>
+      <c r="C152" s="13"/>
+      <c r="D152" s="13"/>
+      <c r="E152" s="13"/>
+      <c r="F152" s="13"/>
+      <c r="G152" s="13"/>
+      <c r="H152" s="13"/>
       <c r="I152" s="14" t="str">
-        <f t="shared" ref="I152:I215" si="6">IF(SUM(B152:F152,H152)=0,"",SUM(B152:F152,H152))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="14" t="str">
-        <f t="shared" ref="J152:J215" si="7">IF(I152="","",1440-I152)</f>
-        <v/>
-      </c>
-      <c r="K152" s="10"/>
-      <c r="L152" s="10"/>
-      <c r="M152" s="10"/>
-      <c r="N152" s="11"/>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="K152" s="15"/>
+      <c r="L152" s="15"/>
+      <c r="M152" s="15"/>
+      <c r="N152" s="16"/>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" s="8"/>
-      <c r="B153" s="9"/>
-      <c r="C153" s="9"/>
-      <c r="D153" s="9"/>
-      <c r="E153" s="9"/>
-      <c r="F153" s="9"/>
-      <c r="G153" s="9"/>
-      <c r="H153" s="9"/>
+      <c r="B153" s="13"/>
+      <c r="C153" s="13"/>
+      <c r="D153" s="13"/>
+      <c r="E153" s="13"/>
+      <c r="F153" s="13"/>
+      <c r="G153" s="13"/>
+      <c r="H153" s="13"/>
       <c r="I153" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -5457,10 +5457,10 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K153" s="10"/>
-      <c r="L153" s="10"/>
-      <c r="M153" s="10"/>
-      <c r="N153" s="11"/>
+      <c r="K153" s="15"/>
+      <c r="L153" s="15"/>
+      <c r="M153" s="15"/>
+      <c r="N153" s="16"/>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" s="8"/>
@@ -5470,7 +5470,7 @@
       <c r="E154" s="13"/>
       <c r="F154" s="13"/>
       <c r="G154" s="13"/>
-      <c r="H154" s="9"/>
+      <c r="H154" s="13"/>
       <c r="I154" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -5479,10 +5479,10 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K154" s="10"/>
-      <c r="L154" s="10"/>
-      <c r="M154" s="10"/>
-      <c r="N154" s="11"/>
+      <c r="K154" s="15"/>
+      <c r="L154" s="15"/>
+      <c r="M154" s="15"/>
+      <c r="N154" s="16"/>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" s="8"/>
@@ -6682,11 +6682,11 @@
       <c r="G209" s="13"/>
       <c r="H209" s="13"/>
       <c r="I209" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I209:I272" si="8">IF(SUM(B209:F209,H209)=0,"",SUM(B209:F209,H209))</f>
         <v/>
       </c>
       <c r="J209" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J209:J272" si="9">IF(I209="","",1440-I209)</f>
         <v/>
       </c>
       <c r="K209" s="15"/>
@@ -6704,11 +6704,11 @@
       <c r="G210" s="13"/>
       <c r="H210" s="13"/>
       <c r="I210" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="15"/>
@@ -6726,11 +6726,11 @@
       <c r="G211" s="13"/>
       <c r="H211" s="13"/>
       <c r="I211" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="15"/>
@@ -6748,11 +6748,11 @@
       <c r="G212" s="13"/>
       <c r="H212" s="13"/>
       <c r="I212" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="15"/>
@@ -6770,11 +6770,11 @@
       <c r="G213" s="13"/>
       <c r="H213" s="13"/>
       <c r="I213" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="15"/>
@@ -6792,11 +6792,11 @@
       <c r="G214" s="13"/>
       <c r="H214" s="13"/>
       <c r="I214" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="15"/>
@@ -6814,11 +6814,11 @@
       <c r="G215" s="13"/>
       <c r="H215" s="13"/>
       <c r="I215" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="15"/>
@@ -6836,11 +6836,11 @@
       <c r="G216" s="13"/>
       <c r="H216" s="13"/>
       <c r="I216" s="14" t="str">
-        <f t="shared" ref="I216:I279" si="8">IF(SUM(B216:F216,H216)=0,"",SUM(B216:F216,H216))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="14" t="str">
-        <f t="shared" ref="J216:J279" si="9">IF(I216="","",1440-I216)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="15"/>
@@ -6981,7 +6981,7 @@
       <c r="N222" s="16"/>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A223" s="8"/>
+      <c r="A223" s="12"/>
       <c r="B223" s="13"/>
       <c r="C223" s="13"/>
       <c r="D223" s="13"/>
@@ -7003,7 +7003,7 @@
       <c r="N223" s="16"/>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A224" s="8"/>
+      <c r="A224" s="12"/>
       <c r="B224" s="13"/>
       <c r="C224" s="13"/>
       <c r="D224" s="13"/>
@@ -7025,7 +7025,7 @@
       <c r="N224" s="16"/>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A225" s="8"/>
+      <c r="A225" s="12"/>
       <c r="B225" s="13"/>
       <c r="C225" s="13"/>
       <c r="D225" s="13"/>
@@ -7047,7 +7047,7 @@
       <c r="N225" s="16"/>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A226" s="8"/>
+      <c r="A226" s="12"/>
       <c r="B226" s="13"/>
       <c r="C226" s="13"/>
       <c r="D226" s="13"/>
@@ -7069,7 +7069,7 @@
       <c r="N226" s="16"/>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A227" s="8"/>
+      <c r="A227" s="12"/>
       <c r="B227" s="13"/>
       <c r="C227" s="13"/>
       <c r="D227" s="13"/>
@@ -7091,7 +7091,7 @@
       <c r="N227" s="16"/>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A228" s="8"/>
+      <c r="A228" s="12"/>
       <c r="B228" s="13"/>
       <c r="C228" s="13"/>
       <c r="D228" s="13"/>
@@ -7113,7 +7113,7 @@
       <c r="N228" s="16"/>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A229" s="8"/>
+      <c r="A229" s="12"/>
       <c r="B229" s="13"/>
       <c r="C229" s="13"/>
       <c r="D229" s="13"/>
@@ -8090,11 +8090,11 @@
       <c r="G273" s="13"/>
       <c r="H273" s="13"/>
       <c r="I273" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I273:I336" si="10">IF(SUM(B273:F273,H273)=0,"",SUM(B273:F273,H273))</f>
         <v/>
       </c>
       <c r="J273" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J273:J336" si="11">IF(I273="","",1440-I273)</f>
         <v/>
       </c>
       <c r="K273" s="15"/>
@@ -8112,11 +8112,11 @@
       <c r="G274" s="13"/>
       <c r="H274" s="13"/>
       <c r="I274" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="15"/>
@@ -8134,11 +8134,11 @@
       <c r="G275" s="13"/>
       <c r="H275" s="13"/>
       <c r="I275" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="15"/>
@@ -8156,11 +8156,11 @@
       <c r="G276" s="13"/>
       <c r="H276" s="13"/>
       <c r="I276" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="15"/>
@@ -8178,11 +8178,11 @@
       <c r="G277" s="13"/>
       <c r="H277" s="13"/>
       <c r="I277" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="15"/>
@@ -8200,11 +8200,11 @@
       <c r="G278" s="13"/>
       <c r="H278" s="13"/>
       <c r="I278" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="15"/>
@@ -8222,11 +8222,11 @@
       <c r="G279" s="13"/>
       <c r="H279" s="13"/>
       <c r="I279" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="15"/>
@@ -8244,11 +8244,11 @@
       <c r="G280" s="13"/>
       <c r="H280" s="13"/>
       <c r="I280" s="14" t="str">
-        <f t="shared" ref="I280:I343" si="10">IF(SUM(B280:F280,H280)=0,"",SUM(B280:F280,H280))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="14" t="str">
-        <f t="shared" ref="J280:J343" si="11">IF(I280="","",1440-I280)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="15"/>
@@ -9498,11 +9498,11 @@
       <c r="G337" s="13"/>
       <c r="H337" s="13"/>
       <c r="I337" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I337:I400" si="12">IF(SUM(B337:F337,H337)=0,"",SUM(B337:F337,H337))</f>
         <v/>
       </c>
       <c r="J337" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J337:J400" si="13">IF(I337="","",1440-I337)</f>
         <v/>
       </c>
       <c r="K337" s="15"/>
@@ -9520,11 +9520,11 @@
       <c r="G338" s="13"/>
       <c r="H338" s="13"/>
       <c r="I338" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="15"/>
@@ -9542,11 +9542,11 @@
       <c r="G339" s="13"/>
       <c r="H339" s="13"/>
       <c r="I339" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="15"/>
@@ -9564,11 +9564,11 @@
       <c r="G340" s="13"/>
       <c r="H340" s="13"/>
       <c r="I340" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="15"/>
@@ -9586,11 +9586,11 @@
       <c r="G341" s="13"/>
       <c r="H341" s="13"/>
       <c r="I341" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="15"/>
@@ -9608,11 +9608,11 @@
       <c r="G342" s="13"/>
       <c r="H342" s="13"/>
       <c r="I342" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="15"/>
@@ -9630,11 +9630,11 @@
       <c r="G343" s="13"/>
       <c r="H343" s="13"/>
       <c r="I343" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="15"/>
@@ -9652,11 +9652,11 @@
       <c r="G344" s="13"/>
       <c r="H344" s="13"/>
       <c r="I344" s="14" t="str">
-        <f t="shared" ref="I344:I407" si="12">IF(SUM(B344:F344,H344)=0,"",SUM(B344:F344,H344))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="14" t="str">
-        <f t="shared" ref="J344:J407" si="13">IF(I344="","",1440-I344)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="15"/>
@@ -10906,11 +10906,11 @@
       <c r="G401" s="13"/>
       <c r="H401" s="13"/>
       <c r="I401" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I401:I412" si="14">IF(SUM(B401:F401,H401)=0,"",SUM(B401:F401,H401))</f>
         <v/>
       </c>
       <c r="J401" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J401:J412" si="15">IF(I401="","",1440-I401)</f>
         <v/>
       </c>
       <c r="K401" s="15"/>
@@ -10928,11 +10928,11 @@
       <c r="G402" s="13"/>
       <c r="H402" s="13"/>
       <c r="I402" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J402" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K402" s="15"/>
@@ -10950,11 +10950,11 @@
       <c r="G403" s="13"/>
       <c r="H403" s="13"/>
       <c r="I403" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J403" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K403" s="15"/>
@@ -10972,11 +10972,11 @@
       <c r="G404" s="13"/>
       <c r="H404" s="13"/>
       <c r="I404" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J404" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K404" s="15"/>
@@ -10994,11 +10994,11 @@
       <c r="G405" s="13"/>
       <c r="H405" s="13"/>
       <c r="I405" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J405" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K405" s="15"/>
@@ -11016,11 +11016,11 @@
       <c r="G406" s="13"/>
       <c r="H406" s="13"/>
       <c r="I406" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J406" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K406" s="15"/>
@@ -11038,11 +11038,11 @@
       <c r="G407" s="13"/>
       <c r="H407" s="13"/>
       <c r="I407" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J407" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K407" s="15"/>
@@ -11060,11 +11060,11 @@
       <c r="G408" s="13"/>
       <c r="H408" s="13"/>
       <c r="I408" s="14" t="str">
-        <f t="shared" ref="I408:I419" si="14">IF(SUM(B408:F408,H408)=0,"",SUM(B408:F408,H408))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J408" s="14" t="str">
-        <f t="shared" ref="J408:J419" si="15">IF(I408="","",1440-I408)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K408" s="15"/>
@@ -11160,160 +11160,6 @@
       <c r="M412" s="15"/>
       <c r="N412" s="16"/>
     </row>
-    <row r="413" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A413" s="12"/>
-      <c r="B413" s="13"/>
-      <c r="C413" s="13"/>
-      <c r="D413" s="13"/>
-      <c r="E413" s="13"/>
-      <c r="F413" s="13"/>
-      <c r="G413" s="13"/>
-      <c r="H413" s="13"/>
-      <c r="I413" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J413" s="14" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K413" s="15"/>
-      <c r="L413" s="15"/>
-      <c r="M413" s="15"/>
-      <c r="N413" s="16"/>
-    </row>
-    <row r="414" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A414" s="12"/>
-      <c r="B414" s="13"/>
-      <c r="C414" s="13"/>
-      <c r="D414" s="13"/>
-      <c r="E414" s="13"/>
-      <c r="F414" s="13"/>
-      <c r="G414" s="13"/>
-      <c r="H414" s="13"/>
-      <c r="I414" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J414" s="14" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K414" s="15"/>
-      <c r="L414" s="15"/>
-      <c r="M414" s="15"/>
-      <c r="N414" s="16"/>
-    </row>
-    <row r="415" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A415" s="12"/>
-      <c r="B415" s="13"/>
-      <c r="C415" s="13"/>
-      <c r="D415" s="13"/>
-      <c r="E415" s="13"/>
-      <c r="F415" s="13"/>
-      <c r="G415" s="13"/>
-      <c r="H415" s="13"/>
-      <c r="I415" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J415" s="14" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K415" s="15"/>
-      <c r="L415" s="15"/>
-      <c r="M415" s="15"/>
-      <c r="N415" s="16"/>
-    </row>
-    <row r="416" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A416" s="12"/>
-      <c r="B416" s="13"/>
-      <c r="C416" s="13"/>
-      <c r="D416" s="13"/>
-      <c r="E416" s="13"/>
-      <c r="F416" s="13"/>
-      <c r="G416" s="13"/>
-      <c r="H416" s="13"/>
-      <c r="I416" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J416" s="14" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K416" s="15"/>
-      <c r="L416" s="15"/>
-      <c r="M416" s="15"/>
-      <c r="N416" s="16"/>
-    </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A417" s="12"/>
-      <c r="B417" s="13"/>
-      <c r="C417" s="13"/>
-      <c r="D417" s="13"/>
-      <c r="E417" s="13"/>
-      <c r="F417" s="13"/>
-      <c r="G417" s="13"/>
-      <c r="H417" s="13"/>
-      <c r="I417" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J417" s="14" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K417" s="15"/>
-      <c r="L417" s="15"/>
-      <c r="M417" s="15"/>
-      <c r="N417" s="16"/>
-    </row>
-    <row r="418" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A418" s="12"/>
-      <c r="B418" s="13"/>
-      <c r="C418" s="13"/>
-      <c r="D418" s="13"/>
-      <c r="E418" s="13"/>
-      <c r="F418" s="13"/>
-      <c r="G418" s="13"/>
-      <c r="H418" s="13"/>
-      <c r="I418" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J418" s="14" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K418" s="15"/>
-      <c r="L418" s="15"/>
-      <c r="M418" s="15"/>
-      <c r="N418" s="16"/>
-    </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A419" s="12"/>
-      <c r="B419" s="13"/>
-      <c r="C419" s="13"/>
-      <c r="D419" s="13"/>
-      <c r="E419" s="13"/>
-      <c r="F419" s="13"/>
-      <c r="G419" s="13"/>
-      <c r="H419" s="13"/>
-      <c r="I419" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J419" s="14" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K419" s="15"/>
-      <c r="L419" s="15"/>
-      <c r="M419" s="15"/>
-      <c r="N419" s="16"/>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -11323,21 +11169,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J419">
+  <conditionalFormatting sqref="J6:J412">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K419" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K412" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L419" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L412" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M419" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M412" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12600717.xlsx
+++ b/12600717.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python CAP776 Excell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3784CD57-9F51-4A86-B424-85A095B5F66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCAB6CD-1ABB-4A3C-AD6E-8C0BC254A7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -365,6 +365,21 @@
   </si>
   <si>
     <t>End of academic week with 7 classes; finished weekly project deliverables and lab tasks.</t>
+  </si>
+  <si>
+    <t>Saturday project development; worked on microservices architecture and Kafka event streams.</t>
+  </si>
+  <si>
+    <t>Sunday rest and planning; reviewed monthly targets and prepared study material for the upcoming week.</t>
+  </si>
+  <si>
+    <t>No classes; dedicated full day to self-study, DSA problem solving, and personal projects.</t>
+  </si>
+  <si>
+    <t>No classes; focused on full-stack feature implementation, testing, and reading.</t>
+  </si>
+  <si>
+    <t>No classes; completed month-end academic review, personal code maintenance, and goal tracking.</t>
   </si>
 </sst>
 </file>
@@ -3174,115 +3189,235 @@
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="8"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="14" t="str">
+    <row r="50" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="8">
+        <v>46291</v>
+      </c>
+      <c r="B50" s="9">
+        <v>510</v>
+      </c>
+      <c r="C50" s="9">
+        <v>60</v>
+      </c>
+      <c r="D50" s="9">
+        <v>180</v>
+      </c>
+      <c r="E50" s="9">
+        <v>150</v>
+      </c>
+      <c r="F50" s="9">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0</v>
+      </c>
+      <c r="H50" s="9">
+        <v>240</v>
+      </c>
+      <c r="I50" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J50" s="14" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J50" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K50" s="10"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
-      <c r="N50" s="11"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="8"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="14" t="str">
+        <v>300</v>
+      </c>
+      <c r="K50" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L50" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="M50" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N50" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="8">
+        <v>46292</v>
+      </c>
+      <c r="B51" s="9">
+        <v>480</v>
+      </c>
+      <c r="C51" s="9">
+        <v>45</v>
+      </c>
+      <c r="D51" s="9">
+        <v>150</v>
+      </c>
+      <c r="E51" s="9">
+        <v>120</v>
+      </c>
+      <c r="F51" s="9">
+        <v>0</v>
+      </c>
+      <c r="G51" s="9">
+        <v>0</v>
+      </c>
+      <c r="H51" s="9">
+        <v>300</v>
+      </c>
+      <c r="I51" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J51" s="14" t="str">
+        <v>1095</v>
+      </c>
+      <c r="J51" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
-      <c r="N51" s="11"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="8"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="14" t="str">
+        <v>345</v>
+      </c>
+      <c r="K51" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L51" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N51" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B52" s="9">
+        <v>510</v>
+      </c>
+      <c r="C52" s="9">
+        <v>60</v>
+      </c>
+      <c r="D52" s="9">
+        <v>210</v>
+      </c>
+      <c r="E52" s="9">
+        <v>180</v>
+      </c>
+      <c r="F52" s="9">
+        <v>0</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0</v>
+      </c>
+      <c r="H52" s="9">
+        <v>240</v>
+      </c>
+      <c r="I52" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J52" s="14" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J52" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K52" s="10"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
-      <c r="N52" s="11"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="8"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="14" t="str">
+        <v>240</v>
+      </c>
+      <c r="K52" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L52" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="M52" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N52" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B53" s="9">
+        <v>480</v>
+      </c>
+      <c r="C53" s="9">
+        <v>45</v>
+      </c>
+      <c r="D53" s="9">
+        <v>180</v>
+      </c>
+      <c r="E53" s="9">
+        <v>150</v>
+      </c>
+      <c r="F53" s="9">
+        <v>0</v>
+      </c>
+      <c r="G53" s="9">
+        <v>0</v>
+      </c>
+      <c r="H53" s="9">
+        <v>270</v>
+      </c>
+      <c r="I53" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J53" s="14" t="str">
+        <v>1125</v>
+      </c>
+      <c r="J53" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
-      <c r="N53" s="11"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="8"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="14" t="str">
+        <v>315</v>
+      </c>
+      <c r="K53" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L53" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="M53" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N53" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B54" s="9">
+        <v>510</v>
+      </c>
+      <c r="C54" s="9">
+        <v>60</v>
+      </c>
+      <c r="D54" s="9">
+        <v>180</v>
+      </c>
+      <c r="E54" s="9">
+        <v>120</v>
+      </c>
+      <c r="F54" s="9">
+        <v>0</v>
+      </c>
+      <c r="G54" s="9">
+        <v>0</v>
+      </c>
+      <c r="H54" s="9">
+        <v>300</v>
+      </c>
+      <c r="I54" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J54" s="14" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J54" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="11"/>
+        <v>270</v>
+      </c>
+      <c r="K54" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L54" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N54" s="11" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="8"/>
